--- a/results/04-2026/beta/contributions-comparison-04-2026.xlsx
+++ b/results/04-2026/beta/contributions-comparison-04-2026.xlsx
@@ -2886,7 +2886,7 @@
         <v>-0.0289055700739013</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.117350200113337</v>
+        <v>-0.499897395595688</v>
       </c>
       <c r="G24" t="n">
         <v>-0.014530714174193</v>
@@ -2949,25 +2949,25 @@
         <v>-0.261464773606026</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.241898475197163</v>
+        <v>-0.139229581720164</v>
       </c>
       <c r="AB24" t="n">
         <v>0.400833075000047</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.641727532450867</v>
+        <v>0.262180996866793</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.00796655275845429</v>
+        <v>-0.373161504158873</v>
       </c>
       <c r="AE24" t="n">
         <v>0.430588072018699</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.639861462947255</v>
+        <v>0.26031492736318</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.00573571057558156</v>
+        <v>-0.089150923320437</v>
       </c>
     </row>
     <row r="25">
@@ -2987,7 +2987,7 @@
         <v>-0.0733698868603123</v>
       </c>
       <c r="F25" t="n">
-        <v>0.013033349568796</v>
+        <v>-0.403643992985071</v>
       </c>
       <c r="G25" t="n">
         <v>-0.030262516077315</v>
@@ -3050,25 +3050,25 @@
         <v>0.272737134010574</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.145924562447469</v>
+        <v>-0.270169588737866</v>
       </c>
       <c r="AB25" t="n">
         <v>0.329046389863244</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.47446466261275</v>
+        <v>0.0598134793214488</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.00344142465917663</v>
+        <v>-0.412652726526158</v>
       </c>
       <c r="AE25" t="n">
         <v>0.353311002340902</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.843278000160834</v>
+        <v>-1.25792918345213</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.332914903533748</v>
+        <v>-0.531464333252592</v>
       </c>
     </row>
     <row r="26">
@@ -3088,7 +3088,7 @@
         <v>-0.0710580054369052</v>
       </c>
       <c r="F26" t="n">
-        <v>0.239406622639966</v>
+        <v>0.0501880171233495</v>
       </c>
       <c r="G26" t="n">
         <v>0.0586159262003014</v>
@@ -3151,25 +3151,25 @@
         <v>0.0657687568511386</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.651809176738972</v>
+        <v>0.463404670727734</v>
       </c>
       <c r="AB26" t="n">
         <v>-0.0604293144674622</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.651789683360029</v>
+        <v>0.463266623529774</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.337293399647586</v>
+        <v>0.148888893636348</v>
       </c>
       <c r="AE26" t="n">
         <v>-0.0591763970314716</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.01724016240157</v>
+        <v>0.828717102571314</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.0951585553325976</v>
+        <v>-0.15052163934381</v>
       </c>
     </row>
     <row r="27">
@@ -3189,13 +3189,13 @@
         <v>-0.177384890887503</v>
       </c>
       <c r="F27" t="n">
-        <v>0.145349181392773</v>
+        <v>0.0906545813014853</v>
       </c>
       <c r="G27" t="n">
         <v>-0.0135823615948663</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0204825031770616</v>
+        <v>0.0530552985300118</v>
       </c>
       <c r="I27" t="n">
         <v>0.25154363993049</v>
@@ -3252,25 +3252,25 @@
         <v>-0.0928836530179101</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.410384135092492</v>
+        <v>0.388300039888712</v>
       </c>
       <c r="AB27" t="n">
         <v>-0.0142040674807482</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.456241218675884</v>
+        <v>0.434153830494396</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.158840495162002</v>
+        <v>0.136756399958222</v>
       </c>
       <c r="AE27" t="n">
         <v>-0.0111204099597507</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0328123392705189</v>
+        <v>0.0107249510890314</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.211658991114627</v>
+        <v>-0.0395430506071521</v>
       </c>
     </row>
     <row r="28">
@@ -3290,13 +3290,13 @@
         <v>-0.176236422781678</v>
       </c>
       <c r="F28" t="n">
-        <v>0.102231761871102</v>
+        <v>0.0320613916729151</v>
       </c>
       <c r="G28" t="n">
         <v>-0.0140897876009744</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0303844116342299</v>
+        <v>0.0611887191445801</v>
       </c>
       <c r="I28" t="n">
         <v>0.0779306099692082</v>
@@ -3353,25 +3353,25 @@
         <v>-0.139873044970078</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.202085233703639</v>
+        <v>0.162760065763167</v>
       </c>
       <c r="AB28" t="n">
         <v>0.0811831420485551</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.343095608249406</v>
+        <v>0.303804069949841</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.12415462373443</v>
+        <v>0.0848294557939591</v>
       </c>
       <c r="AE28" t="n">
         <v>0.0769225021751926</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0205162722113488</v>
+        <v>-0.0187752660882153</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.0568226934306508</v>
+        <v>-0.109315598970001</v>
       </c>
     </row>
     <row r="29">
@@ -3391,13 +3391,13 @@
         <v>-0.199946813675512</v>
       </c>
       <c r="F29" t="n">
-        <v>0.101672286414703</v>
+        <v>-0.0227724580374239</v>
       </c>
       <c r="G29" t="n">
         <v>-0.00902915102977396</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0272086052503855</v>
+        <v>0.024763706910763</v>
       </c>
       <c r="I29" t="n">
         <v>-0.0522916142007128</v>
@@ -3454,25 +3454,25 @@
         <v>-0.140839771734219</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.0742234180974693</v>
+        <v>-0.0527043427898117</v>
       </c>
       <c r="AB29" t="n">
         <v>0.104915517060876</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.239056667938165</v>
+        <v>0.112269577286512</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.126515032298182</v>
+        <v>-0.000412728589098861</v>
       </c>
       <c r="AE29" t="n">
         <v>0.0962839648399452</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.0677660088396269</v>
+        <v>-0.19455309949128</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.250700691260953</v>
+        <v>0.156528422020213</v>
       </c>
     </row>
     <row r="30">
@@ -3492,13 +3492,13 @@
         <v>-0.186214773942108</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.16686215403164</v>
+        <v>-0.291860335754416</v>
       </c>
       <c r="G30" t="n">
         <v>-0.00871948653904214</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0369848894040224</v>
+        <v>0.0345883706468194</v>
       </c>
       <c r="I30" t="n">
         <v>-0.266873947521892</v>
@@ -3555,25 +3555,25 @@
         <v>-0.139951506095078</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.398953680402588</v>
+        <v>-0.52666917896959</v>
       </c>
       <c r="AB30" t="n">
         <v>0.18995088856399</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.148199934352975</v>
+        <v>-0.275658655070582</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.132079732880696</v>
+        <v>-0.259795231447698</v>
       </c>
       <c r="AE30" t="n">
         <v>0.187576667029949</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.448390226636853</v>
+        <v>-0.575848947354461</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.115706905998653</v>
+        <v>-0.194613090461231</v>
       </c>
     </row>
     <row r="31">
@@ -3593,13 +3593,13 @@
         <v>-0.18074145350152</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0313851804324279</v>
+        <v>-0.15535957088525</v>
       </c>
       <c r="G31" t="n">
         <v>-0.00433211445750534</v>
       </c>
       <c r="H31" t="n">
-        <v>0.043787785295544</v>
+        <v>0.0414325973251567</v>
       </c>
       <c r="I31" t="n">
         <v>-0.36382241629954</v>
@@ -3656,25 +3656,25 @@
         <v>-0.136187107329353</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.350169750618483</v>
+        <v>-0.476931589288372</v>
       </c>
       <c r="AB31" t="n">
         <v>0.0706728660628411</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.219234135309988</v>
+        <v>-0.345900938412574</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0136526656810571</v>
+        <v>-0.113109172988833</v>
       </c>
       <c r="AE31" t="n">
         <v>0.0709967202450261</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.497504370160331</v>
+        <v>-0.624171173262917</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.248286083356366</v>
+        <v>-0.353337121549218</v>
       </c>
     </row>
     <row r="32">
@@ -3694,13 +3694,13 @@
         <v>-0.188023408655981</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0445220451969919</v>
+        <v>0.0910626909637126</v>
       </c>
       <c r="G32" t="n">
         <v>-0.000926599399724825</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0392387337096022</v>
+        <v>0.0369153856606749</v>
       </c>
       <c r="I32" t="n">
         <v>-0.386429275379733</v>
@@ -3757,25 +3757,25 @@
         <v>-0.145161352331443</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.297987909831869</v>
+        <v>-0.253608567858958</v>
       </c>
       <c r="AB32" t="n">
         <v>0.0195130068435475</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.278413218041402</v>
+        <v>-0.23404305869826</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0884413655478634</v>
+        <v>0.132820707520774</v>
       </c>
       <c r="AE32" t="n">
         <v>0.014475621392602</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.570591322945622</v>
+        <v>-0.52622116360248</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.396062982145609</v>
+        <v>-0.480198595927784</v>
       </c>
     </row>
     <row r="33">
@@ -3795,13 +3795,13 @@
         <v>-0.184495417794735</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0625721612707403</v>
+        <v>0.128834675525228</v>
       </c>
       <c r="G33" t="n">
         <v>0.0107213802706063</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0439168865394133</v>
+        <v>0.0416283220440629</v>
       </c>
       <c r="I33" t="n">
         <v>-0.42871696202656</v>
@@ -3858,25 +3858,25 @@
         <v>-0.143061358041577</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.304709825738888</v>
+        <v>-0.240484032811458</v>
       </c>
       <c r="AB33" t="n">
         <v>-0.00912811548088149</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.313867481114126</v>
+        <v>-0.249635464504215</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.124007136287672</v>
+        <v>0.188232929215102</v>
       </c>
       <c r="AE33" t="n">
         <v>-0.0130690619856717</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.670358881669258</v>
+        <v>-0.606126865059347</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.546711200353016</v>
+        <v>-0.583092037319801</v>
       </c>
     </row>
     <row r="34">
@@ -3896,13 +3896,13 @@
         <v>-0.183578043716544</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0621279186476758</v>
+        <v>-0.0139896774285151</v>
       </c>
       <c r="G34" t="n">
         <v>0.00704988013781239</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0255593448966518</v>
+        <v>0.0233003782332651</v>
       </c>
       <c r="I34" t="n">
         <v>-0.616876171778661</v>
@@ -3959,25 +3959,25 @@
         <v>-0.143181122174836</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.636152946721656</v>
+        <v>-0.589995381969783</v>
       </c>
       <c r="AB34" t="n">
         <v>-0.10280007135667</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.739646784072489</v>
+        <v>-0.693438933785944</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.0192767749429954</v>
+        <v>0.0268807898088781</v>
       </c>
       <c r="AE34" t="n">
         <v>-0.10280007135667</v>
       </c>
       <c r="AF34" t="n">
-        <v>-1.12836625498998</v>
+        <v>-1.08215840470343</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.716705207441297</v>
+        <v>-0.709669401657044</v>
       </c>
     </row>
   </sheetData>
@@ -4080,9 +4080,15 @@
         <v>28</v>
       </c>
       <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4096,36 +4102,96 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
+      <c r="D2" t="n">
+        <v>0.151665919024954</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.275728132113999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.155024098137774</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0399948728920478</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0244008508451835</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.00119703520847525</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.076563950863772</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0140722303353539</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0653396753473717</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.00950220027496541</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.00000824561118694087</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.0335089344402273</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.065417829213983</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.185757421025787</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.241636630113166</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.0917203334476128</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.133565386955577</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.0419897826631274</v>
+      </c>
       <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2"/>
+        <v>-0.0917203334476128</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.133565386955577</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.46938383380208</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.577601160588483</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -4138,87 +4204,95 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.75484353727292</v>
+        <v>2.05306150321667</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.124279288081753</v>
+        <v>-0.613352860863573</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.58052103264709</v>
+        <v>0.163255603902112</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.20981982366178</v>
+        <v>0.0488379551020667</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.352430727434125</v>
+        <v>0.0128552657625797</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0481838240428069</v>
+        <v>-0.00653711251943106</v>
       </c>
       <c r="K3" t="n">
-        <v>3.99676589301536</v>
+        <v>0.431733104280873</v>
       </c>
       <c r="L3" t="n">
-        <v>0.901897549439133</v>
+        <v>0.0257708249999914</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.54826691311574</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.30592391986787</v>
       </c>
       <c r="P3" t="n">
-        <v>0.48120371954258</v>
+        <v>0.621676593207357</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0802030019952744</v>
+        <v>0.65956395718011</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.31104714606541</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.124466550251368</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.00000986356452146503</v>
       </c>
       <c r="W3" t="n">
-        <v>0.631075385824842</v>
+        <v>0.372769979146812</v>
       </c>
       <c r="X3" t="n">
-        <v>0.465267635936778</v>
+        <v>-0.160080769289425</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.95562828679108</v>
+        <v>3.8369353291202</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0765054614364146</v>
+        <v>-2.39722668676711</v>
       </c>
       <c r="AA3" t="n">
-        <v>-12.6129341273791</v>
+        <v>0.218260041490563</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.40760861988374</v>
+        <v>8.74486573546583</v>
       </c>
       <c r="AC3" t="n">
-        <v>-5.26645178102681</v>
+        <v>8.9309395294461</v>
       </c>
       <c r="AD3" t="n">
-        <v>-7.14557460638148</v>
-      </c>
-      <c r="AE3"/>
+        <v>0.218260041490563</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>8.62039918521447</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>10.3706481717992</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.00961320689186</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -4228,90 +4302,98 @@
         <v>34</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.02999570545342</v>
+        <v>-1.05968043898936</v>
       </c>
       <c r="E4" t="n">
-        <v>0.662439060586808</v>
+        <v>-0.640329109700446</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.29148877764927</v>
+        <v>0.475021182587629</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.10144738499591</v>
+        <v>0.0790187713359683</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.356022580048501</v>
+        <v>0.0143221335174119</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0483694602063134</v>
+        <v>-0.0157296886192294</v>
       </c>
       <c r="K4" t="n">
-        <v>3.78577193945112</v>
+        <v>1.26713389785588</v>
       </c>
       <c r="L4" t="n">
-        <v>0.942430420303678</v>
+        <v>0.0132274861551893</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-4.04640526560572</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.54141848999307</v>
       </c>
       <c r="P4" t="n">
-        <v>0.299440277263877</v>
+        <v>0.612029460935782</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0719172901690351</v>
+        <v>1.23557600797968</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.0386990383207061</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.199552742055976</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.0000638572111890291</v>
       </c>
       <c r="W4" t="n">
-        <v>0.625095437352693</v>
+        <v>0.248951251691522</v>
       </c>
       <c r="X4" t="n">
-        <v>0.480888259480678</v>
+        <v>-0.0421729893599904</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.25346585506587</v>
+        <v>-1.63537359312616</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.885909210199254</v>
+        <v>-0.064635955563641</v>
       </c>
       <c r="AA4" t="n">
-        <v>-5.90227830166986</v>
+        <v>0.552346472186169</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.07452236856964</v>
+        <v>5.16139327319511</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.588464569920177</v>
+        <v>5.69127333718764</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.220907925053565</v>
-      </c>
-      <c r="AE4"/>
+        <v>0.552346472186169</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4.96184053113914</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.99126378849784</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.83799587371516</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -4321,91 +4403,97 @@
         <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.614797877170335</v>
+        <v>-0.099842630261638</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.117743787428055</v>
+        <v>-0.165887510045688</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.03806526870992</v>
+        <v>-0.386194152613053</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.98519753015624</v>
+        <v>-0.182435353405305</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.315429524502341</v>
+        <v>0.0109469268007227</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0425626112791961</v>
+        <v>-0.0103599849377959</v>
       </c>
       <c r="K5" t="n">
-        <v>3.68893800814695</v>
+        <v>0.450604648232777</v>
       </c>
       <c r="L5" t="n">
-        <v>0.930030407204698</v>
+        <v>0.0209904625994305</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.07589086500759</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.97492899568704</v>
       </c>
       <c r="P5" t="n">
-        <v>0.28867976808967</v>
+        <v>-0.386007431151805</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0650050644519994</v>
+        <v>0.223340052285071</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.0440089932827624</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.137038091934644</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.0000329691175003333</v>
       </c>
       <c r="W5" t="n">
-        <v>0.599897709613419</v>
+        <v>0.384174159984565</v>
       </c>
       <c r="X5" t="n">
-        <v>0.474097944118684</v>
+        <v>-0.176484339194978</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.632263478993916</v>
+        <v>-0.331735217356747</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.100278185604474</v>
+        <v>0.0660050770494209</v>
       </c>
       <c r="AA5" t="n">
-        <v>-5.47447942305503</v>
+        <v>-0.568772712361355</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.91832337883146</v>
+        <v>-2.35235872955152</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.832285058834112</v>
+        <v>-2.93502940425967</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0997433942357216</v>
+        <v>-0.568772712361355</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.70623082177305</v>
+        <v>-2.48939682148616</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-3.200759544567</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.90763406238303</v>
       </c>
     </row>
     <row r="6">
@@ -4419,88 +4507,94 @@
         <v>-1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.94577300106344</v>
+        <v>1.09302262488195</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.166836816120495</v>
+        <v>-0.314255664680673</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.39501081011423</v>
+        <v>-0.210000955927445</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.16487343802734</v>
+        <v>0.040191811227022</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.374203095070054</v>
+        <v>-0.0146310491062612</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0512158006339589</v>
+        <v>-0.00894800957383496</v>
       </c>
       <c r="K6" t="n">
-        <v>0.539188126292998</v>
+        <v>1.20739338339323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.148811599959799</v>
+        <v>0.00676794952274797</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.78605426127284</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.7120539680953</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.0720891195621463</v>
       </c>
       <c r="P6" t="n">
-        <v>0.225434102169575</v>
+        <v>-0.0276230801741278</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0573954849633155</v>
+        <v>0.26790265385701</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.137553374125125</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.127466485750547</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.00181557790265906</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0263239526360397</v>
+        <v>0.228447862578173</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0736493045414841</v>
+        <v>0.0456274330040622</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.79269514952129</v>
+        <v>1.35163182855064</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.319914667662646</v>
+        <v>-0.572864868349367</v>
       </c>
       <c r="AA6" t="n">
-        <v>-6.0920538583392</v>
+        <v>-0.193345941150108</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06653322994088</v>
+        <v>7.93378769759511</v>
       </c>
       <c r="AC6" t="n">
-        <v>-4.95442242360361</v>
+        <v>7.75569645454409</v>
       </c>
       <c r="AD6" t="n">
-        <v>-7.06703224078754</v>
+        <v>-0.193345941150108</v>
       </c>
       <c r="AE6" t="n">
-        <v>-3.47298888196993</v>
+        <v>7.80632121184456</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8.53446341474537</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.92390395761885</v>
       </c>
     </row>
     <row r="7">
@@ -4514,88 +4608,94 @@
         <v>-1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.895259553739619</v>
+        <v>-0.760837094445061</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0181622599935816</v>
+        <v>-0.449748443088805</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.11919934931381</v>
+        <v>-0.210775058191278</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.05151591144452</v>
+        <v>0.0169408295689168</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.350569555145588</v>
+        <v>-0.0379640320507537</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0478611465369624</v>
+        <v>-0.0150262613159189</v>
       </c>
       <c r="K7" t="n">
-        <v>0.302926708608305</v>
+        <v>-0.196686348313314</v>
       </c>
       <c r="L7" t="n">
-        <v>0.111874118609287</v>
+        <v>-0.0017442878601428</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.313127440827752</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.18699888715633</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.0569219024109985</v>
       </c>
       <c r="P7" t="n">
-        <v>0.190429161095224</v>
+        <v>-0.206577491174076</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0539630575106287</v>
+        <v>0.497923824425357</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.0480788527973548</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.0475306717473889</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.138666598140122</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.0702033823773491</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.00768650492141917</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0187652236164013</v>
+        <v>-0.13831785472286</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0719839269836023</v>
+        <v>0.257610701467474</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.643077841189523</v>
+        <v>-0.287610782304056</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.270343972543678</v>
+        <v>-0.92297475522981</v>
       </c>
       <c r="AA7" t="n">
-        <v>-5.66643772994743</v>
+        <v>-0.24689103402653</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.747554768571927</v>
+        <v>-1.00963271046716</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.87038895056381</v>
+        <v>-1.25880069434664</v>
       </c>
       <c r="AD7" t="n">
-        <v>-5.78381076429701</v>
+        <v>-0.24689103402653</v>
       </c>
       <c r="AE7" t="n">
-        <v>-3.13254792144882</v>
+        <v>-1.07983609284451</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-2.46938623188051</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.71389535669892</v>
       </c>
     </row>
     <row r="8">
@@ -4609,88 +4709,94 @@
         <v>-1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.598143343869283</v>
+        <v>-0.65559298655779</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.215242734688881</v>
+        <v>-0.249965501812647</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.05169131114216</v>
+        <v>-0.275346977517997</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.05484406844295</v>
+        <v>0.0303190711719823</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.326361793929932</v>
+        <v>-0.0425207530530465</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0484931591913802</v>
+        <v>-0.0275043102567617</v>
       </c>
       <c r="K8" t="n">
-        <v>0.357146543637793</v>
+        <v>-0.0837905995481597</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0704587476438306</v>
+        <v>0.0101907315282219</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-1.16326668661122</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.0464480781910861</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1.05781751166181</v>
       </c>
       <c r="P8" t="n">
-        <v>0.100498488206915</v>
+        <v>-0.36096248063431</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0465484811388895</v>
+        <v>0.278814237851361</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.194257994799614</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.00815768600713234</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.142944627710033</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.029074626310537</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.00122944518445003</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0208951065399506</v>
+        <v>0.0605652903172054</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0711291108271835</v>
+        <v>-0.0643627476458901</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.843029328677745</v>
+        <v>-0.610993309907876</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0296432501195813</v>
+        <v>-0.29456517846256</v>
       </c>
       <c r="AA8" t="n">
-        <v>-5.57633769639015</v>
+        <v>-0.31515314337929</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.664962488221669</v>
+        <v>-2.06113735720888</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.86855701739158</v>
+        <v>-2.38279100305357</v>
       </c>
       <c r="AD8" t="n">
-        <v>-5.68194309594975</v>
+        <v>-0.31515314337929</v>
       </c>
       <c r="AE8" t="n">
-        <v>-4.60826067669964</v>
+        <v>-2.09021198351942</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-3.28834949142401</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.106007963281536</v>
       </c>
     </row>
     <row r="9">
@@ -4704,88 +4810,94 @@
         <v>-1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.56809377111169</v>
+        <v>0.0779110721791147</v>
       </c>
       <c r="E9" t="n">
-        <v>0.232992818400793</v>
+        <v>-0.47724837154047</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.17136590835325</v>
+        <v>-0.173498804599885</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.15188623190715</v>
+        <v>0.0655390793395653</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.331215298044626</v>
+        <v>-0.0475026428300258</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0498035493462144</v>
+        <v>-0.0533073753537703</v>
       </c>
       <c r="K9" t="n">
-        <v>0.315260962649935</v>
+        <v>0.2049388395681</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0579535876404212</v>
+        <v>-0.00782536629873107</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.409363174402356</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.24177525935871</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-1.14362647421813</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0264857596494269</v>
+        <v>-0.152351935921463</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0495014492620225</v>
+        <v>0.0766559451513306</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.0499195953792768</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.0883559748539155</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.15386764165396</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.0257986939403195</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.00060286888446617</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0291274939667533</v>
+        <v>-0.0231810529779638</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0848563719448032</v>
+        <v>-0.028599393048954</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.64633269925718</v>
+        <v>0.329994696071855</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.311231746546286</v>
+        <v>-0.72933199543321</v>
       </c>
       <c r="AA9" t="n">
-        <v>-5.80503158012897</v>
+        <v>-0.208789857580898</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.562023414430846</v>
+        <v>-2.42092105160786</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.20604931145143</v>
+        <v>-2.63468816179706</v>
       </c>
       <c r="AD9" t="n">
-        <v>-6.54115026416233</v>
+        <v>-0.208789857580898</v>
       </c>
       <c r="AE9" t="n">
-        <v>-6.26848409129916</v>
+        <v>-2.44671974554818</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-3.03402546115842</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.0643244424293917</v>
       </c>
     </row>
     <row r="10">
@@ -4799,88 +4911,94 @@
         <v>-1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0204160855947682</v>
+        <v>-0.694809928191332</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.265074523423107</v>
+        <v>-0.226992137141287</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.295987366250525</v>
+        <v>-0.703014969234408</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.239258118110003</v>
+        <v>-0.0585793509828508</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.331847185649429</v>
+        <v>-0.0636914765269768</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0529668837411546</v>
+        <v>-0.0494560919258956</v>
       </c>
       <c r="K10" t="n">
-        <v>0.311963246317278</v>
+        <v>-0.783527475192377</v>
       </c>
       <c r="L10" t="n">
-        <v>0.029776834533985</v>
+        <v>-0.0213617014404082</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-0.0808652201663875</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.0389165118704214</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-1.04225136296652</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0232597671021929</v>
+        <v>-0.151859290281068</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0614606775476687</v>
+        <v>-0.149171277984238</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0.0367012373824597</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.0543822312571854</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.129849330467061</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.0143072227949861</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.000669126063992638</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00833652048047577</v>
+        <v>0.0442724220334607</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0891513378327853</v>
+        <v>-0.090904806150079</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.0296667520781785</v>
+        <v>-0.328141854263953</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.214991685750161</v>
+        <v>-0.593660211068666</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.923373080414281</v>
+        <v>-0.876075859460641</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.523025283922365</v>
+        <v>-2.16798383433384</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.394914978632665</v>
+        <v>-3.06339026497288</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.639573416461004</v>
+        <v>-0.876075859460641</v>
       </c>
       <c r="AE10" t="n">
-        <v>-4.66161938521752</v>
+        <v>-2.18229105712882</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-3.9851923303055</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-3.19423837869211</v>
       </c>
     </row>
     <row r="11">
@@ -4894,88 +5012,94 @@
         <v>-1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0751082618322529</v>
+        <v>-0.399157394958232</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.457647701451241</v>
+        <v>-0.268944525809951</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.466555102655951</v>
+        <v>-0.873820442565869</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.362748852055029</v>
+        <v>-0.214664512569586</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.331939518541749</v>
+        <v>-0.0803342153487852</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0523730990995568</v>
+        <v>-0.0337428082423864</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.15583638520348</v>
+        <v>0.0173513012103416</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0304189068509981</v>
+        <v>-0.00659370025694457</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-1.08780132662658</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.0286618549846008</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-1.54646806325821</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0528922510180057</v>
+        <v>-0.191860299071128</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0590266510950542</v>
+        <v>-0.247822624049822</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.0261434048470381</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.0328721598759834</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.0888286293902712</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.0170524557288868</v>
       </c>
       <c r="V11" t="n">
-        <v>0.00173285779654201</v>
+        <v>-0.000823667305731244</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0192893793966968</v>
+        <v>-0.0682460391169559</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0790779748546257</v>
+        <v>-0.0603932141150797</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.108563469369141</v>
+        <v>0.369773746805842</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.273975970249848</v>
+        <v>-1.03787566757402</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.21933298535589</v>
+        <v>-1.20568398792863</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0867745173698923</v>
+        <v>-3.11959610857322</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.13136385351591</v>
+        <v>-4.36239862308495</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.51390329313489</v>
+        <v>-1.20568398792863</v>
       </c>
       <c r="AE11" t="n">
-        <v>-3.59414251742699</v>
+        <v>-3.10254365284433</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-5.03050054385313</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-3.83451695668526</v>
       </c>
     </row>
     <row r="12">
@@ -4989,88 +5113,94 @@
         <v>-1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.31626927940953</v>
+        <v>-0.242823096678381</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0282691490748419</v>
+        <v>0.106453660909352</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.131481650174329</v>
+        <v>-0.587518114932699</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2408922048595</v>
+        <v>0.0496954101018784</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.319124916841571</v>
+        <v>-0.0802162167568417</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.0769149503246465</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0508034989609651</v>
+        <v>-0.039581832979608</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.065131230567256</v>
+        <v>-0.465686475963213</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0236488487907349</v>
+        <v>0.0620959573956428</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-0.029239519915622</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.0313133754874284</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0.996238538018657</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0934261179098455</v>
+        <v>-0.053586117886107</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0687903077718204</v>
+        <v>-0.206711173283088</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.0257542154874665</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0.0658638096362217</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.051777688642237</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0.0117706301818196</v>
       </c>
       <c r="V12" t="n">
-        <v>0.00142270707850328</v>
+        <v>-0.000123762004087371</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0177446269716689</v>
+        <v>0.0527845221121613</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0910805824430793</v>
+        <v>-0.0495107428308193</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1.87345304357477</v>
+        <v>-0.614947240942878</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.414547086759919</v>
+        <v>0.478577805173849</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.744416800724806</v>
+        <v>-0.580579627213782</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0442716365327439</v>
+        <v>-1.72627805103759</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.699770211974808</v>
+        <v>-2.31716754988747</v>
       </c>
       <c r="AD12" t="n">
-        <v>-2.9877703423095</v>
+        <v>-0.657494577538429</v>
       </c>
       <c r="AE12" t="n">
-        <v>-2.92059932901693</v>
+        <v>-1.71450742085577</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-2.4535369856565</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-3.62581383024339</v>
       </c>
     </row>
     <row r="13">
@@ -5084,88 +5214,94 @@
         <v>-1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.240317456945671</v>
+        <v>0.408127157390506</v>
       </c>
       <c r="E13" t="n">
-        <v>0.255187440113125</v>
+        <v>-0.131517823949666</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.215318610133234</v>
+        <v>-0.359533121155637</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.246612121957976</v>
+        <v>0.13817168563911</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.355491687599291</v>
+        <v>-0.0662309339104978</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.0497535662897082</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0559150843776331</v>
+        <v>-0.0451622756893484</v>
       </c>
       <c r="K13" t="n">
-        <v>0.703004440125746</v>
+        <v>-0.085948771694519</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00895955917403384</v>
+        <v>0.245744048760629</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.0178413315986848</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.017764517588567</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-0.399304760187622</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.217560933278485</v>
+        <v>-0.0168691475009429</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0626602174594977</v>
+        <v>-0.104922259192415</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0.0366540693142568</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0.0658846439556142</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.036091410141793</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0.0106794377000554</v>
       </c>
       <c r="V13" t="n">
-        <v>0.00132751132925747</v>
+        <v>-0.000109722496949621</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0257698381285965</v>
+        <v>0.00411887924544264</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0521303109585909</v>
+        <v>0.0875326979593281</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.623843993604467</v>
+        <v>-0.268021120898531</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.638713976771921</v>
+        <v>0.544630454339372</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.876232218515985</v>
+        <v>-0.282595033045533</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.637082037015657</v>
+        <v>-0.45442319460995</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.233008498030292</v>
+        <v>-0.73836697138364</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.218138514862837</v>
+        <v>-0.332348599335242</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1.33984639169206</v>
+        <v>-0.443743756909895</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.4617576379428</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-2.98274687443948</v>
       </c>
     </row>
     <row r="14">
@@ -5179,88 +5315,94 @@
         <v>-1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.224076459579734</v>
+        <v>0.0986211102479304</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.182065868422935</v>
+        <v>0.16159780704795</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.512313083683776</v>
+        <v>0.45815738974538</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.156353448696189</v>
+        <v>0.142414615890442</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0535892594105925</v>
+        <v>-0.086884822835906</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.352688858412503</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.012245042898891</v>
+        <v>-0.0459491813670316</v>
       </c>
       <c r="K14" t="n">
-        <v>0.602482199849019</v>
+        <v>-0.135716291989542</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0240289345266572</v>
+        <v>0.00260669857259059</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-0.535705680958679</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.0174617678654437</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.404461445912231</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.177426612746528</v>
+        <v>-0.0259682197266134</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0080772406093929</v>
+        <v>-0.0872748338841096</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0.0363373998048857</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0.0494736596430556</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.092457615134267</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0.0104974524138563</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0011707433153768</v>
+        <v>-0.000311140436700266</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0205505250406361</v>
+        <v>0.0460597523323344</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0390146497663111</v>
+        <v>0.0995642627388841</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.187474497778229</v>
+        <v>-0.0628285716925441</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.145463906621431</v>
+        <v>0.323047488988425</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.735876884956473</v>
+        <v>0.818846407620433</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.470812822708706</v>
+        <v>-1.25281556342879</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.261242264801396</v>
+        <v>-0.423500585246295</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.219231673644598</v>
+        <v>0.46615754920793</v>
       </c>
       <c r="AE14" t="n">
-        <v>-1.23476095598796</v>
+        <v>-1.24231811101493</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.163281667950414</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-2.02726920885071</v>
       </c>
     </row>
     <row r="15">
@@ -5274,88 +5416,94 @@
         <v>-1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.06364969431804</v>
+        <v>-0.17522834363671</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.309412988246061</v>
+        <v>0.28349848506119</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.266372335252147</v>
+        <v>0.442379584928365</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0569071821253413</v>
+        <v>0.20744084444904</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0201715482528461</v>
+        <v>-0.0799994595193902</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.234874630908832</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.00884337609402773</v>
+        <v>-0.0402728319746563</v>
       </c>
       <c r="K15" t="n">
-        <v>0.529703655053397</v>
+        <v>-0.138697976544072</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0518278232178437</v>
+        <v>-0.0423019778213649</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0.251107279261999</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.425173808942275</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.284346518329023</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.133206880057373</v>
+        <v>0.0206078171681824</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.00194668513320788</v>
+        <v>-0.366636157886361</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.000280267206246567</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0.0421999455564572</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.0966840653399767</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0.00875374801846945</v>
       </c>
       <c r="V15" t="n">
-        <v>0.00089020534624607</v>
+        <v>-0.000901417786342305</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0200256794054023</v>
+        <v>0.148467345637757</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0449721043006873</v>
+        <v>0.103560064389503</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.971805814056666</v>
+        <v>-0.268486583650671</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.401256868507433</v>
+        <v>0.37675672507515</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.238376577163629</v>
+        <v>0.762928566953573</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.409403837237641</v>
+        <v>-1.39123103603504</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.172162073829759</v>
+        <v>-0.617103421087763</v>
       </c>
       <c r="AD15" t="n">
-        <v>-1.20090060873434</v>
+        <v>0.528053936044742</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.15651028488782</v>
+        <v>-1.38247728801657</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.508833279663284</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.89685239280325</v>
       </c>
     </row>
     <row r="16">
@@ -5369,88 +5517,94 @@
         <v>-1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7906634507001</v>
+        <v>0.265114129328331</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0719183519448354</v>
+        <v>0.163168056962309</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.183648978894682</v>
+        <v>0.153012138687469</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0374892707434003</v>
+        <v>0.11855270408997</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00706060829683716</v>
+        <v>-0.056916093561604</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.230313539714713</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.00556154807282366</v>
+        <v>-0.0325384939709171</v>
       </c>
       <c r="K16" t="n">
-        <v>0.510440603185104</v>
+        <v>-0.0630686413692216</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0623655798792373</v>
+        <v>-0.100441752908905</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.0334849857528701</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.00837607895158873</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.130659331395125</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.0876892513562236</v>
+        <v>0.0443633276094131</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.0152965985340333</v>
+        <v>-0.380432018291749</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.000373893073066147</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.027069676356541</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.0966627805616126</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.138607631498054</v>
       </c>
       <c r="V16" t="n">
-        <v>0.000852838362823442</v>
+        <v>-0.0000746366255718586</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0400619570721799</v>
+        <v>-0.103313938667222</v>
       </c>
       <c r="X16" t="n">
-        <v>0.00957456791287075</v>
+        <v>0.243113207232247</v>
       </c>
       <c r="Y16" t="n">
-        <v>-2.08567689857237</v>
+        <v>-0.172354520046453</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.3669317998171</v>
+        <v>0.600636706337094</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.144578026441662</v>
+        <v>0.412030542300483</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.396259251229904</v>
+        <v>-0.796177903897253</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.252344381512292</v>
+        <v>-0.380727188578476</v>
       </c>
       <c r="AD16" t="n">
-        <v>-1.46640071724298</v>
+        <v>0.18171700258577</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.776167878621189</v>
+        <v>-0.657570272399199</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.047554997712165</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.271579396961083</v>
       </c>
     </row>
     <row r="17">
@@ -5461,91 +5615,97 @@
         <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.269514682028253</v>
+        <v>0.045448168517171</v>
       </c>
       <c r="E17" t="n">
-        <v>0.192146794690886</v>
+        <v>0.29252165195858</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.202651265079971</v>
+        <v>0.121206326418866</v>
       </c>
       <c r="G17" t="n">
-        <v>0.117297896094173</v>
+        <v>0.0713566379112017</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0117520761233097</v>
+        <v>-0.0695617412404508</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.0818676169398049</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.00739691428315027</v>
+        <v>-0.0367854553710071</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.185293507601626</v>
+        <v>-0.227021554254278</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0508505824541685</v>
+        <v>-0.255115519387006</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.00681132392888474</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.00743692980912469</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.056530793171545</v>
+        <v>0.0248039845495032</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.0158199659950282</v>
+        <v>-0.166622762057952</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-0.00591654338862635</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.0268158280524225</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.096959286606789</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.113129553553935</v>
       </c>
       <c r="V17" t="n">
-        <v>0.000786911953811258</v>
+        <v>-0.0000545598146086757</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0432487550072168</v>
+        <v>0.0367521777136748</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0346670984618538</v>
+        <v>0.0702317523530833</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.145954516537685</v>
+        <v>0.250026258743084</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0685866292003172</v>
+        <v>0.0879435617326674</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.104244753486394</v>
+        <v>0.168106654503534</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.229846643450323</v>
+        <v>-0.776344234660777</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.334371128050155</v>
+        <v>-0.60685770938353</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.411739015387523</v>
+        <v>0.0862390375637294</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.82456800375236</v>
+        <v>-0.663214681106842</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.268887888907778</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.223361959702328</v>
       </c>
     </row>
     <row r="18">
@@ -5556,91 +5716,97 @@
         <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.65009085907779</v>
+        <v>-0.118888769480967</v>
       </c>
       <c r="E18" t="n">
-        <v>0.182280411680468</v>
+        <v>0.0578492685203659</v>
       </c>
       <c r="F18" t="n">
-        <v>0.24428357077464</v>
+        <v>0.524011303989962</v>
       </c>
       <c r="G18" t="n">
-        <v>0.419311333897339</v>
+        <v>0.226257619100136</v>
       </c>
       <c r="H18" t="n">
-        <v>0.079768725405358</v>
+        <v>-0.0583421771791422</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.126429969506553</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00192559093618451</v>
+        <v>-0.0306234177436169</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.146846727652624</v>
+        <v>-0.0391971812109982</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.21013688402024</v>
+        <v>-0.0264468900302406</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.112216462199238</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.00141532562528259</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0530655342703733</v>
+        <v>0.014484214265143</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.0486109581579828</v>
+        <v>-0.14954092655211</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-0.00672015447733912</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.0376925192139727</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.063526397197148</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.104799481735209</v>
       </c>
       <c r="V18" t="n">
-        <v>0.000669474609434011</v>
+        <v>-0.000591101276562183</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0400187734123923</v>
+        <v>-0.15853006033471</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.0182790122719496</v>
+        <v>0.127457693502973</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.0982397094863</v>
+        <v>-0.171780249704384</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.265868438728042</v>
+        <v>0.110740748743783</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.743456892941205</v>
+        <v>0.78628460647213</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.330330391410003</v>
+        <v>-0.559877459260424</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.415996712887084</v>
+        <v>0.231049610408206</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24836798364534</v>
+        <v>0.659854636965577</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.457668089429875</v>
+        <v>-0.455077977525216</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.170010109447605</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.140039015352823</v>
       </c>
     </row>
     <row r="19">
@@ -5651,91 +5817,97 @@
         <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5171206183264</v>
+        <v>0.103341456976986</v>
       </c>
       <c r="E19" t="n">
-        <v>0.194177371141737</v>
+        <v>0.0173938205137982</v>
       </c>
       <c r="F19" t="n">
-        <v>0.162177040364865</v>
+        <v>0.380078089898013</v>
       </c>
       <c r="G19" t="n">
-        <v>0.376783547552911</v>
+        <v>0.196826924579495</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0679044882179801</v>
+        <v>-0.0450770336700762</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.0936476749635413</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0000525620062131734</v>
+        <v>-0.0222319818500852</v>
       </c>
       <c r="K19" t="n">
-        <v>0.120190997751939</v>
+        <v>0.158676333630306</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.193847279438661</v>
+        <v>0.0184243290004525</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.105054220876667</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.00067289277251629</v>
       </c>
       <c r="P19" t="n">
-        <v>0.134419632178539</v>
+        <v>0.0122711555885737</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.0560133505749712</v>
+        <v>-0.347544264331175</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-0.0169307840414787</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.0360553862964996</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.0503808377656664</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.096310570246564</v>
       </c>
       <c r="V19" t="n">
-        <v>0.00046050287990348</v>
+        <v>-0.0021680855276638</v>
       </c>
       <c r="W19" t="n">
-        <v>0.0526248404908935</v>
+        <v>-0.124825687677082</v>
       </c>
       <c r="X19" t="n">
-        <v>0.00182481649610173</v>
+        <v>0.109836183969317</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.385667979013946</v>
+        <v>0.166035250882516</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.0627247318292825</v>
+        <v>-0.045299973391732</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.605731937241117</v>
+        <v>0.602362580528956</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0600602352257011</v>
+        <v>-0.48090178331643</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.665389417396461</v>
+        <v>0.12447112969564</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.342446170211798</v>
+        <v>0.508714905565415</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.0718313946933406</v>
+        <v>-0.384591213069866</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.245206407186424</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.048470906359604</v>
       </c>
     </row>
     <row r="20">
@@ -5746,91 +5918,97 @@
         <v>34</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0990278191602723</v>
+        <v>0.388607859372138</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.510142273801707</v>
+        <v>0.106717242058178</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0936088796793244</v>
+        <v>0.293353894435985</v>
       </c>
       <c r="G20" t="n">
-        <v>0.260218406885932</v>
+        <v>0.0350150955007453</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0141694096701895</v>
+        <v>-0.0420529614264801</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.0944311286144539</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.00495469646316644</v>
+        <v>-0.0118438471670446</v>
       </c>
       <c r="K20" t="n">
-        <v>0.361127490746317</v>
+        <v>0.244501518441326</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.129412444419439</v>
+        <v>0.0479555043783489</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.100674585445191</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.000334428480009475</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0786950116174199</v>
+        <v>0.0101537453217768</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.0447357144970942</v>
+        <v>-0.310717582891275</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-0.0668181934008458</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0.0341431987177175</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.0440281009267043</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.0553398426809612</v>
       </c>
       <c r="V20" t="n">
-        <v>0.000433874456352825</v>
+        <v>-0.0000481981319541984</v>
       </c>
       <c r="W20" t="n">
-        <v>0.0628434050224072</v>
+        <v>0.192074034349464</v>
       </c>
       <c r="X20" t="n">
-        <v>0.01513616904824</v>
+        <v>0.0420686719463712</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.752291713319673</v>
+        <v>0.612848820878669</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.143121620357693</v>
+        <v>-0.117523719448353</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.362738295028274</v>
+        <v>0.180384979214747</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.34431378194842</v>
+        <v>-0.0742382360498926</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.705674203483611</v>
+        <v>0.106286927910456</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0965041105216311</v>
+        <v>0.274816107829201</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.318894812247811</v>
+        <v>-0.0188983933689314</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.601612029340773</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.186985164266756</v>
       </c>
     </row>
     <row r="21">
@@ -5841,91 +6019,97 @@
         <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0812341124203805</v>
+        <v>0.120411772392591</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.381423157515817</v>
+        <v>0.0185956746460551</v>
       </c>
       <c r="F21" t="n">
-        <v>0.157004669642865</v>
+        <v>0.284736384341645</v>
       </c>
       <c r="G21" t="n">
-        <v>0.291546588589109</v>
+        <v>0.0391411302137562</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0609413512552768</v>
+        <v>-0.0330895642945137</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.134337351020563</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0032221884355319</v>
+        <v>0.0118677357398302</v>
       </c>
       <c r="K21" t="n">
-        <v>0.431348136915539</v>
+        <v>0.258468976489482</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.101646273313768</v>
+        <v>0.0156718199149948</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.100513671211502</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.000172659142950679</v>
       </c>
       <c r="P21" t="n">
-        <v>0.157531162691926</v>
+        <v>0.00554609587831411</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.0342426707783961</v>
+        <v>-0.155135119864267</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>-0.0291085616047994</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0.0223558203170651</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.0265684363093117</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.0302912288977294</v>
       </c>
       <c r="V21" t="n">
-        <v>0.000390881580531054</v>
+        <v>-0.0000584549268793934</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0692344703182424</v>
+        <v>0.138952681402228</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0266150729066513</v>
+        <v>0.148998237211467</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.360231641634757</v>
+        <v>0.135250550861866</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.660420686730194</v>
+        <v>0.00375689617678003</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.511830180754072</v>
+        <v>0.168699850674615</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.548792827958941</v>
+        <v>0.203974334374208</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.05729346354625</v>
+        <v>0.37231700923784</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.757104418450818</v>
+        <v>0.303037201695179</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.611105670707397</v>
+        <v>0.234265563271938</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.511324456276486</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.382038250562822</v>
       </c>
     </row>
     <row r="22">
@@ -5936,91 +6120,97 @@
         <v>34</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.801848553958979</v>
+        <v>-0.533648503397823</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1002430572737</v>
+        <v>-0.0596293518013056</v>
       </c>
       <c r="F22" t="n">
-        <v>0.234070284444802</v>
+        <v>-0.0494368359564461</v>
       </c>
       <c r="G22" t="n">
-        <v>0.22274314897062</v>
+        <v>0.056172172525477</v>
       </c>
       <c r="H22" t="n">
-        <v>0.112001122131426</v>
+        <v>-0.00295807996764376</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.115307261317255</v>
       </c>
       <c r="J22" t="n">
-        <v>0.00758450981940631</v>
+        <v>0.0140842526424371</v>
       </c>
       <c r="K22" t="n">
-        <v>0.374808429243634</v>
+        <v>0.167406742873536</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0715798125129062</v>
+        <v>-0.0102730128711663</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.0969680156800284</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.616671536616394</v>
+        <v>0.000205664283505596</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.0268903962769402</v>
+        <v>-0.0742311351787579</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>-0.0281630611185205</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-0.0150150468139017</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.0106418570513199</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-0.0297652241785434</v>
       </c>
       <c r="V22" t="n">
-        <v>0.000448026822755992</v>
+        <v>-0.000305138334205149</v>
       </c>
       <c r="W22" t="n">
-        <v>0.086572216698976</v>
+        <v>0.0925385175650943</v>
       </c>
       <c r="X22" t="n">
-        <v>0.115226001724134</v>
+        <v>0.000551965031565569</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.642611663076624</v>
+        <v>-1.18817041587178</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.941006166391344</v>
+        <v>0.59489256067265</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.575189619490833</v>
+        <v>-0.0973949910447126</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.23287295602411</v>
+        <v>-0.00437632570967921</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.80006792430157</v>
+        <v>-0.101775817864685</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.09846242761629</v>
+        <v>0.0179122702725422</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.823629281700134</v>
+        <v>0.0253888984688642</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-0.695053673063814</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.165772304934967</v>
       </c>
     </row>
     <row r="23">
@@ -6034,88 +6224,94 @@
         <v>-1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.738567888165026</v>
+        <v>-0.496499803263801</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.770553692961448</v>
+        <v>0.0906579245430833</v>
       </c>
       <c r="F23" t="n">
-        <v>1.26126425353839</v>
+        <v>-0.46199816785084</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0203582884478025</v>
+        <v>-0.0393993485224859</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0616492217827958</v>
+        <v>0.0070494530187146</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.216923374445816</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.00111826557545844</v>
+        <v>0.00192006564289267</v>
       </c>
       <c r="K23" t="n">
-        <v>0.659742296913906</v>
+        <v>0.467337261391294</v>
       </c>
       <c r="L23" t="n">
-        <v>0.115283844579485</v>
+        <v>-0.0144940802134268</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>-0.0949495613552628</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.933982107053682</v>
+        <v>0.001826348170756</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.0234722842131928</v>
+        <v>-0.0949962807277038</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-0.0267370903938112</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-0.0134831467879264</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.0100206453912311</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>-0.0233356501478242</v>
       </c>
       <c r="V23" t="n">
-        <v>0.00135061026762014</v>
+        <v>-0.00103802633880351</v>
       </c>
       <c r="W23" t="n">
-        <v>0.103618847477065</v>
+        <v>0.285091465526087</v>
       </c>
       <c r="X23" t="n">
-        <v>0.104927907374086</v>
+        <v>-0.0299392802978311</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.00461491352782</v>
+        <v>-0.945848277891172</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.504506667598656</v>
+        <v>0.540006399170454</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.3410178301661</v>
+        <v>-0.274529505412121</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88307220334397</v>
+        <v>0.445899379286268</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.19619575018294</v>
+        <v>-0.0273475251368821</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.68707416905646</v>
+        <v>-0.491452879857937</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1597862814113</v>
+        <v>0.469235029434092</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.4331894038576</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-0.00382664782603897</v>
       </c>
     </row>
     <row r="24">
@@ -6129,88 +6325,94 @@
         <v>-1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.785421952888642</v>
+        <v>0.027039500570289</v>
       </c>
       <c r="E24" t="n">
-        <v>0.272215608951232</v>
+        <v>-0.0289055700739013</v>
       </c>
       <c r="F24" t="n">
-        <v>0.456271360957227</v>
+        <v>-0.499897395595688</v>
       </c>
       <c r="G24" t="n">
-        <v>0.113036826205113</v>
+        <v>-0.014530714174193</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0164967979433802</v>
+        <v>0.126456632364786</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.233931922438709</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.00908890529066499</v>
+        <v>0.0132545562346545</v>
       </c>
       <c r="K24" t="n">
-        <v>0.265641618335417</v>
+        <v>0.237596042876202</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0627983063373826</v>
+        <v>-0.0470710449582601</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>-0.00101193337338092</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.602316614675793</v>
+        <v>-0.000248954063931031</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.0252627472050739</v>
+        <v>-0.0726907376615534</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>-0.0264334674541418</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-0.0139545112674622</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-0.0086306387520275</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>-0.0297549970186519</v>
       </c>
       <c r="V24" t="n">
-        <v>0.00104628542694577</v>
+        <v>-0.0000539507371187338</v>
       </c>
       <c r="W24" t="n">
-        <v>0.0837478054897792</v>
+        <v>0.316532912689999</v>
       </c>
       <c r="X24" t="n">
-        <v>0.0634711404794532</v>
+        <v>0.0465164147221872</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.47790062118474</v>
+        <v>0.259598704102414</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.420263059344869</v>
+        <v>-0.261464773606026</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.57611855545398</v>
+        <v>-0.139229581720164</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05020944199541</v>
+        <v>0.400833075000047</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.61981799799282</v>
+        <v>0.262180996866793</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.6774555598327</v>
+        <v>-0.373161504158873</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.80502414373907</v>
+        <v>0.430588072018699</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.26031492736318</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>-0.089150923320437</v>
       </c>
     </row>
     <row r="25">
@@ -6224,88 +6426,94 @@
         <v>-1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.170401721573954</v>
+        <v>-1.24437277591327</v>
       </c>
       <c r="E25" t="n">
-        <v>0.289268068293533</v>
+        <v>-0.0733698868603123</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.28767715742693</v>
+        <v>-0.403643992985071</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0523730750748418</v>
+        <v>-0.030262516077315</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03369519624896</v>
+        <v>0.0122688877326342</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.142483137788292</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.00676879283553745</v>
+        <v>0.0187005366381567</v>
       </c>
       <c r="K25" t="n">
-        <v>0.184406349608803</v>
+        <v>0.137992081379504</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0746178403969059</v>
+        <v>-0.0270462024830238</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-0.000970325921589451</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.126070291699692</v>
+        <v>-0.00226084286508445</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.0185952466797741</v>
+        <v>-0.0556893589221825</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>-0.00389812728397777</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-0.0128484986125136</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-0.0076726144240776</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>-0.0242890509138495</v>
       </c>
       <c r="V25" t="n">
-        <v>0.000930085148769297</v>
+        <v>-0.0000531438557844164</v>
       </c>
       <c r="W25" t="n">
-        <v>0.0878940460426715</v>
+        <v>0.283001238493291</v>
       </c>
       <c r="X25" t="n">
-        <v>0.074310977373599</v>
+        <v>0.0427711776553399</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.309937634547031</v>
+        <v>-1.59047979678416</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.428803981266609</v>
+        <v>0.272737134010574</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.208140358846628</v>
+        <v>-0.259838890856755</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.528473931337605</v>
+        <v>0.329022042419087</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.321541830241735</v>
+        <v>0.0700839628014538</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.440408176961314</v>
+        <v>-0.402322028645047</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.72585008336669</v>
+        <v>0.353311093332936</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-1.24765869997213</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>-0.528896712382591</v>
       </c>
     </row>
     <row r="26">
@@ -6313,94 +6521,100 @@
         <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.729748572667767</v>
+        <v>1.66614404825135</v>
       </c>
       <c r="E26" t="n">
-        <v>0.193304762420189</v>
+        <v>-0.188704745478899</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.00346257886530601</v>
+        <v>-0.0227340968335049</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.135645125238271</v>
+        <v>0.028247717760595</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0156563096827323</v>
+        <v>0.0230908327045624</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.313134521728542</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0183040457154303</v>
+        <v>0.0167727057307057</v>
       </c>
       <c r="K26" t="n">
-        <v>0.382543621269901</v>
+        <v>-0.0399401532635637</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0579394532111995</v>
+        <v>0.0328468378633532</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>-0.000947267993169992</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.0542597946996714</v>
+        <v>-0.0102942452796516</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.0109885989240814</v>
+        <v>-0.019590885584065</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>-0.00268390951436379</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-0.0143869288496247</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>-0.00710978917847009</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>-0.0223516886372291</v>
       </c>
       <c r="V26" t="n">
-        <v>0.000909983979662897</v>
+        <v>-0.000517122684655328</v>
       </c>
       <c r="W26" t="n">
-        <v>0.108266015362494</v>
+        <v>0.22476206195789</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0483974906100803</v>
+        <v>0.0229002032225388</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.87377276020949</v>
+        <v>1.61468392753924</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.337328949961912</v>
+        <v>-0.137244624766788</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.173127528963333</v>
+        <v>0.358361790668108</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.53217230957295</v>
+        <v>0.162837776260205</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.360045387338738</v>
+        <v>0.580582306938243</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.17639842290884</v>
+        <v>0.0452272689395654</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.15713487073541</v>
+        <v>0.185189464897434</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.05802160971069</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.159372108311035</v>
       </c>
     </row>
     <row r="27">
@@ -6408,37 +6622,37 @@
         <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.445952395275734</v>
+        <v>-0.420709831037319</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.20166892189541</v>
+        <v>-0.176184247400425</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0892506234089735</v>
+        <v>-0.0565006293763161</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.172868233488136</v>
+        <v>-0.00880150241652977</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0149494078240388</v>
+        <v>0.020506223308859</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.251833673563064</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0166343036204765</v>
+        <v>0.0123004390178763</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.0654559090140964</v>
+        <v>-0.18964298329505</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0351477326195404</v>
+        <v>0.0473865174312755</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -6450,52 +6664,58 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.142238602747249</v>
+        <v>-0.00899748036153736</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.0109728265138488</v>
+        <v>-0.0144565211050625</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>-0.00223770188924322</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-0.00983310836289468</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>-0.00646591694202064</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>-0.0205297639592623</v>
       </c>
       <c r="V27" t="n">
-        <v>0.000550697470559348</v>
+        <v>-0.000434869020035866</v>
       </c>
       <c r="W27" t="n">
-        <v>0.111790327825205</v>
+        <v>0.214079581465423</v>
       </c>
       <c r="X27" t="n">
-        <v>0.00930447938418269</v>
+        <v>0.0322655618445932</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.541880209286643</v>
+        <v>-0.505498412760509</v>
       </c>
       <c r="Z27" t="n">
-        <v>-1.1057411078845</v>
+        <v>-0.0913956656772347</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.293977270667197</v>
+        <v>0.219438889884077</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.061675448686465</v>
+        <v>0.0415761599621467</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.355860540487222</v>
+        <v>0.320919075194145</v>
       </c>
       <c r="AD27" t="n">
-        <v>-2.00348185765836</v>
+        <v>-0.0323947836789873</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.234495864056701</v>
+        <v>0.0621059239214089</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.275975003243598</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.198675708464536</v>
       </c>
     </row>
     <row r="28">
@@ -6503,37 +6723,37 @@
         <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.246811552537029</v>
+        <v>-0.150858146592394</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.701023189739022</v>
+        <v>-0.175043552790665</v>
       </c>
       <c r="F28" t="n">
-        <v>0.118312109100465</v>
+        <v>-0.109557240622333</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.000256539523891115</v>
+        <v>-0.0116662370392203</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00246092563533082</v>
+        <v>0.0304195921974103</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.0780207605778426</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0139095068623302</v>
+        <v>0.0108989230434262</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.00148757516808802</v>
+        <v>-0.00546385491572805</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.00293844135063176</v>
+        <v>0.0544809327441534</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -6545,52 +6765,58 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.191734408357009</v>
+        <v>-0.00970680057072466</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.0101848152148561</v>
+        <v>-0.0126215734177798</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>-0.00281262448770808</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>-0.00668782996714076</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>-0.00574772632456763</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>-0.019447025589517</v>
       </c>
       <c r="V28" t="n">
-        <v>0.000435364990230677</v>
+        <v>-0.000402619731988997</v>
       </c>
       <c r="W28" t="n">
-        <v>0.0847174083631458</v>
+        <v>0.170716249234254</v>
       </c>
       <c r="X28" t="n">
-        <v>0.0394804443813704</v>
+        <v>-0.0297158643115744</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.104183938468055</v>
+        <v>-0.187456851853127</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.843650803807996</v>
+        <v>-0.138444847529932</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.10662271288786</v>
+        <v>-0.00178253435925942</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.0814959754563956</v>
+        <v>0.132676576504906</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.0252232099316704</v>
+        <v>0.190896539488912</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.922611532344381</v>
+        <v>-0.079803294937102</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.665520908987568</v>
+        <v>0.152123602094423</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.135005159894147</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.099845686650204</v>
       </c>
     </row>
     <row r="29">
@@ -6598,37 +6824,37 @@
         <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.236293839912024</v>
+        <v>-0.110173388408814</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.500581822861104</v>
+        <v>-0.198593458052039</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0975244785756879</v>
+        <v>-0.0938691318649901</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0386258246811041</v>
+        <v>-0.00721340500497764</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0284032451436045</v>
+        <v>0.0272401105490608</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-0.0523522549602245</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0103414453057861</v>
+        <v>0.0116792142668356</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.00106503725991371</v>
+        <v>0.0351930300938164</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.0332876508409643</v>
+        <v>0.0589448427500478</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -6640,52 +6866,58 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.200182977952781</v>
+        <v>-0.00922620457866887</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.00648973503533466</v>
+        <v>-0.00855857232959935</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>-0.000293382507181051</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>-0.00303213847028566</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>-0.0031681598427723</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>-0.0123226453887189</v>
       </c>
       <c r="V29" t="n">
-        <v>0.000403050377109946</v>
+        <v>-0.000371559930609723</v>
       </c>
       <c r="W29" t="n">
-        <v>0.0776811919344377</v>
+        <v>0.116915450722698</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.00701085960325653</v>
+        <v>-0.0152025009432854</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.172712476819678</v>
+        <v>-0.169527870704099</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.564163185953451</v>
+        <v>-0.139238975756754</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.0769930863054353</v>
+        <v>-0.11451878982377</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.169851623007681</v>
+        <v>0.158844757937732</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.0927161310955723</v>
+        <v>0.104518673248615</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.829591793868701</v>
+        <v>-0.0621665348635455</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.983020901695072</v>
+        <v>0.171167403326451</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.204248173212239</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.360698318340177</v>
       </c>
     </row>
     <row r="30">
@@ -6693,37 +6925,37 @@
         <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0491681555954095</v>
+        <v>-0.11749209491152</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0968520350921813</v>
+        <v>-0.184954364701993</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0218584541588953</v>
+        <v>-0.346033074678445</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0215869043043168</v>
+        <v>-0.00701225480204403</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0027125401154728</v>
+        <v>0.0370277067636871</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>-0.267184694661036</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0129928246231732</v>
+        <v>0.0117504457810699</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.200298790846424</v>
+        <v>0.0295327400207467</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.0331562866868593</v>
+        <v>0.00839718520675031</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -6735,52 +6967,58 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.188196868711145</v>
+        <v>-0.00442812281376111</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.000426848125865568</v>
+        <v>-0.00792813540768285</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>-0.000286302962534931</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>-0.00134832978737942</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>-0.00178157103577599</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>-0.011697636380997</v>
       </c>
       <c r="V30" t="n">
-        <v>0.000335624655608717</v>
+        <v>-0.000322956686060288</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0677193559961637</v>
+        <v>0.114722443042679</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.0315130699031937</v>
+        <v>-0.00711649746668697</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.197317027534432</v>
+        <v>-0.163987462838498</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.245000907031204</v>
+        <v>-0.138458996775016</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.0154290486787386</v>
+        <v>-0.572162185606492</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.385038153258451</v>
+        <v>0.117745548833549</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.40053136791322</v>
+        <v>-0.39370107053356</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.352847488416449</v>
+        <v>-0.304977490945456</v>
       </c>
       <c r="AE30" t="n">
-        <v>-1.02713316807197</v>
+        <v>0.129443185214546</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0.696147530147073</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>-0.327843966624264</v>
       </c>
     </row>
     <row r="31">
@@ -6788,37 +7026,37 @@
         <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.185931673717807</v>
+        <v>-0.100537913769166</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.108297414744336</v>
+        <v>-0.179518090858253</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.586093253054394</v>
+        <v>-0.20875387886039</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0208388227617696</v>
+        <v>-0.00274072405671313</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0232223637287399</v>
+        <v>0.0438384716842681</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-0.364246832230586</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.0164746020022437</v>
+        <v>0.0103326017155023</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.104642246784481</v>
+        <v>0.0366137137752495</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.0204568047680984</v>
+        <v>0.00890406050198482</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -6830,52 +7068,58 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.267210080263024</v>
+        <v>-0.00142312480846168</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.00438960477574218</v>
+        <v>-0.00805673466147888</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>-0.000279932204496591</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>-0.00101864471012829</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>-0.00149913524971762</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>-0.00978076307697897</v>
       </c>
       <c r="V31" t="n">
-        <v>0.000168865832942323</v>
+        <v>-0.000315600107555253</v>
       </c>
       <c r="W31" t="n">
-        <v>0.0634577248745407</v>
+        <v>0.0616095842025686</v>
       </c>
       <c r="X31" t="n">
-        <v>0.0487122409529696</v>
+        <v>-0.0109793532176722</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.115383477846206</v>
+        <v>-0.145311068813816</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.0377492188727359</v>
+        <v>-0.134744935813603</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.647036037400005</v>
+        <v>-0.522068802934925</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.275506892264749</v>
+        <v>0.0737743822701202</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.924518891096745</v>
+        <v>-0.387884392606698</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.846884632123275</v>
+        <v>-0.157821970704339</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.737983861688202</v>
+        <v>0.0835551453470992</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-0.667940397234117</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>-0.425835315121894</v>
       </c>
     </row>
     <row r="32">
@@ -6883,37 +7127,37 @@
         <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0744074671289783</v>
+        <v>-0.107368263247405</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.428206600593838</v>
+        <v>-0.186750757530558</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.13761295504619</v>
+        <v>0.0304640223038154</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0476091265716088</v>
+        <v>0.000540224260864334</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0132332335235895</v>
+        <v>0.0392841583391929</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>-0.386880253005743</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0145344515951972</v>
+        <v>0.00998641367971701</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0276786238743035</v>
+        <v>0.0380736733973169</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.000258650982775115</v>
+        <v>0.00935610800823099</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -6925,52 +7169,58 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.329935222920469</v>
+        <v>0.000358589023948943</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.00962015015352939</v>
+        <v>-0.00827285943507663</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>-0.000274482203485652</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>-0.00100236810299272</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>-0.00123904489460494</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.024935854277618</v>
       </c>
       <c r="V32" t="n">
-        <v>0.000182806814545433</v>
+        <v>-0.000309363502687192</v>
       </c>
       <c r="W32" t="n">
-        <v>0.0655157766078311</v>
+        <v>0.009435814340737</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.034281765045955</v>
+        <v>-0.0222591298571621</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.244032163500842</v>
+        <v>-0.150436010658066</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.597831296965702</v>
+        <v>-0.143683010119898</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.213122159006955</v>
+        <v>-0.306295695814262</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.31675300278699</v>
+        <v>0.0488050922305394</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.53062639625145</v>
+        <v>-0.257331537250197</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.88442552971631</v>
+        <v>0.0805845571914808</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.728437361031184</v>
+        <v>0.0238692379529214</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-0.551450558028161</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>-0.529946664655398</v>
       </c>
     </row>
     <row r="33">
@@ -6978,37 +7228,37 @@
         <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.595958500738521</v>
+        <v>-0.177302710484615</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.301471364217713</v>
+        <v>-0.183246646150979</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.206007240290697</v>
+        <v>0.0689203379959541</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0627010221796822</v>
+        <v>0.0120712992194414</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.0518062913360866</v>
+        <v>0.0439677222278218</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>-0.429217694598965</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.0209679761928949</v>
+        <v>0.0109394892890476</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0509909536931962</v>
+        <v>0.00242889478013606</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0142492816465207</v>
+        <v>0.00976637754758537</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -7020,148 +7270,96 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.202571254951709</v>
+        <v>0.00259276018795545</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0459765626085517</v>
+        <v>-0.00564681216626738</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>0.000198529911872401</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>-0.000993960416273958</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>-0.000240277831537949</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>0.0218518238394764</v>
       </c>
       <c r="V33" t="n">
-        <v>0.00017853752784391</v>
+        <v>-0.000302765050606375</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0636565975595412</v>
+        <v>-0.00291588534563375</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.0417490944149862</v>
+        <v>-0.0121918619904309</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.864576523049736</v>
+        <v>-0.218931602374652</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.0328533419064989</v>
+        <v>-0.141617754260942</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.341851383672215</v>
+        <v>-0.292759150299271</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.17112700257835</v>
+        <v>0.0145498294332267</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.513620883083582</v>
+        <v>-0.278163943760303</v>
       </c>
       <c r="AD33" t="n">
-        <v>-1.41105074803982</v>
+        <v>0.136458544299694</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.873802099573963</v>
+        <v>-0.00730199440624964</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>-0.638713300395896</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>-0.638562946451312</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
         <v>67</v>
       </c>
-      <c r="B34" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-0.305782919810542</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.405456123270805</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-0.209574260715635</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0256024111111773</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-0.0569224788485525</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>-0.0102762198245453</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-0.0715942909753495</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.00750152970804745</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>-0.194463260158895</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.0197142618091516</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.000120185196341277</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.0484573454787984</v>
-      </c>
-      <c r="X34" t="n">
-        <v>-0.0164894270461889</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>-0.301472162384577</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>-0.40976688069677</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>-0.25125558713006</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>-0.20673525696225</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>-0.458573463777045</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>-1.16981250685839</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>-1.07804335418445</v>
-      </c>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+      <c r="S34"/>
+      <c r="T34"/>
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+      <c r="Y34"/>
+      <c r="Z34"/>
+      <c r="AA34"/>
+      <c r="AB34"/>
+      <c r="AC34"/>
+      <c r="AD34"/>
+      <c r="AE34"/>
+      <c r="AF34"/>
+      <c r="AG34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7263,9 +7461,15 @@
         <v>28</v>
       </c>
       <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -7277,36 +7481,96 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="n">
-        <v>0.46938383380208</v>
-      </c>
-      <c r="AE2"/>
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -7317,87 +7581,95 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.80790504048959</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.48907357278182</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7.7437766365492</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.25865777876385</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.365285993196705</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0416467115233758</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.56503278873449</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.876126724439142</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.54826691311574</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.30592391986787</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.140472873664777</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.579360955184836</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.31104714606541</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.124466550251368</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00000986356452146503</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.25830540667803</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.625348405226203</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.79256361591128</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2.47373214820352</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.8311941688697</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.33725711558209</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.1973913104729</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.5162227781807</v>
-      </c>
-      <c r="AE3"/>
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -7405,90 +7677,98 @@
       </c>
       <c r="B4"/>
       <c r="C4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.02968473353594</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.30276817028725</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7665099602369</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18046615633188</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.370344713565913</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.032639771587084</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.51863804159524</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.929202934148489</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.04640526560572</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.54141848999307</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.312589183671905</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.16365871781065</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0386990383207061</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.199552742055976</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0000638572111890291</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.376144185661171</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.523061248840668</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.38190773806029</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.950545165762895</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.45462477385603</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.913129095374529</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.10280876726746</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.77035586344428</v>
-      </c>
-      <c r="AE4"/>
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -7496,91 +7776,97 @@
       </c>
       <c r="B5"/>
       <c r="C5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.514955246908697</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.048143722617633</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2.65187111609687</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.80276217675093</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.326376451303064</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0322026263414002</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.23833335991417</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.909039944605267</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.07589086500759</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.97492899568704</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.674687199241475</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.158334987833072</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0440089932827624</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.137038091934644</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0000329691175003333</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.215723549628854</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.650582283313662</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.300528261637169</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.166283262653895</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.90570671069367</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-8.27068210838298</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.76731446309378</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3.30050293880272</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>4.61386488415608</v>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7592,88 +7878,94 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3.03879562594539</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.147418848560178</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3.18500985418678</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.20506524925436</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.359572045963793</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0422677910601239</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.668205257100232</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.142043650437051</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.78605426127284</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7120539680953</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0720891195621463</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.253057182343703</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.210507168893695</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.137553374125125</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.127466485750547</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00181557790265906</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.202123909942133</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0280218715374219</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.14432697807193</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.252950200686721</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.89870791718909</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.86725446765423</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.7101188781477</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.6014956555329</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>8.39689283958878</v>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7685,88 +7977,94 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.134422459294558</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.431586183095223</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2.90842429112253</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.06845674101344</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.312605523094834</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0328348852210435</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.499613056921619</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.11361840646943</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.313127440827752</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.18699888715633</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0569219024109985</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3970066522693</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.443960766914728</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0480788527973548</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0475306717473889</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.138666598140122</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0702033823773491</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00768650492141917</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.157083078339261</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.185626774483872</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.355467058885467</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.652630782686132</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.4195466959209</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.75718747903909</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.61158825621717</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.3144245324165</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>4.84644327814774</v>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7778,88 +8076,94 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0574496426885069</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.034722767123766</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.77634433362416</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08516313961493</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.283841040876885</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0209888489346185</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.440937143185953</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0602680161156087</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.16326668661122</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0464480781910861</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.05781751166181</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.461460968841225</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.232265756712472</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.194257994799614</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00815768600713234</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.142944627710033</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.029074626310537</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.00122944518445003</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0396701837772548</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.135491858473074</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.232036018769869</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.324208428582141</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.26118455301086</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.72609984543055</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.48576601433801</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.39359360452574</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>4.5022527134181</v>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7871,88 +8175,94 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6460048432908</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.710241189941263</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.99786710375337</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.21742531124672</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2837126552146</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0035038260075559</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.110322123081835</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0657789539391523</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.409363174402356</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.24177525935871</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.14362647421813</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.17883769557089</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0271544958893081</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0499195953792768</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0883559748539155</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.15386764165396</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0257986939403195</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.00060286888446617</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0523085469447171</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.113455764993757</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.97632739532904</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.0405637419795</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.59624172254807</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.98294446603871</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.57136114965437</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.50712480300391</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>6.20415964886977</v>
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -7964,88 +8274,94 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7152260137861</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03808238628182</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.407027602983883</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.180678767127152</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.268155709122452</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00351079181525901</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.09549072150965</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0511385359743932</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0808652201663875</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0389165118704214</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.04225136296652</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.175119057383261</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.210631955531907</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.0367012373824597</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0543822312571854</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.129849330467061</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0143072227949861</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.000669126063992638</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0359359015529849</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.180056143982864</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.298475102185774</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.378668525318505</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04729722095364</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.69100911825621</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.66847528634022</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>-3.3456189138445</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.46738100652541</v>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -8057,88 +8373,94 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.474265656790485</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.18870317564129</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.407265339909918</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.148084339485443</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.251605303192964</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0186302908571704</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.173187686413822</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0370126071079427</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.08780132662658</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0286618549846008</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.54646806325821</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.244752550089134</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.306849275144876</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0261434048470381</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0328721598759834</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0888286293902712</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0170524557288868</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.00255652510227325</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0875354185136527</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.139471188969705</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.478337216174983</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.763899697324172</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01364899742726</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.20637062594311</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-3.23103476956904</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>-3.51659725071824</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.24037443925827</v>
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -8150,88 +8472,94 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2.07344618273115</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0781845118345101</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.45603646475837</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.290587614961378</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.238908700084729</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0769149503246465</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0112216659813571</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.400555245395957</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0384471086049079</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.029239519915622</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0313133754874284</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.996238538018657</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0398400000237385</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.275501481054908</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0257542154874665</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0658638096362217</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.051777688642237</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0117706301818196</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.00154646908259065</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0350398951404924</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.140591325273899</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25850580263189</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.893124891933768</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.163837173511024</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.77054968757033</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.61739733791266</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.534233356653</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.70521450122646</v>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8243,88 +8571,94 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.648444614336177</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.386705264062791</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.144214511022403</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.384783807597086</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.289260753688793</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0497535662897082</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0107528086882847</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.788953211820265</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.236784489586595</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0178413315986848</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.017764517588567</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.399304760187622</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.200691785777542</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.167582476651913</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.0366540693142568</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0658846439556142</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.036091410141793</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0106794377000554</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.00143723382620709</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0216509588831539</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0354023870007372</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.355822872705936</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.094083522432549</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.593637185470452</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.09150523162561</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.505358473353348</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.243619123079963</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1.64290048274742</v>
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8336,88 +8670,94 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.125455349331804</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.343663675470885</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.970470473429156</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.298768064586631</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0332955634253135</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.352688858412503</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0337041384681406</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.738198491838561</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0266356330992478</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.535705680958679</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0174617678654437</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.404461445912231</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.151458393019915</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.0953520744935025</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.0363373998048857</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0494736596430556</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.092457615134267</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0104974524138563</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.00148188375207707</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0255092272916983</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.060549612972573</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.250303069470773</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.468511395609856</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55472329257691</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.7236283861375</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.162258320444899</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.055950005694184</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.79250825286275</v>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8429,88 +8769,94 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.88842135068133</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.592911473307251</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.708751920180512</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.150533662323699</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0598279112665441</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.234874630908832</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0314294558806286</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.668401631597469</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00952584539647881</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.251107279261999</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.425173808942275</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.284346518329023</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.153814697225555</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.364689472753153</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.000280267206246567</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0421999455564572</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0966840653399767</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.00875374801846945</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.00179162313258838</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.128441666232355</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0585879600888157</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.703319230405995</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.778013593582583</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.0013051441172</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.80063487327268</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.789265494917522</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.692067329071056</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.25965789208457</v>
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8522,88 +8868,94 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2.05577758002843</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0912497050174736</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.336661117582151</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0810634333465697</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0639767018584412</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.230313539714713</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0269769458980934</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.573509244554326</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0380761730296677</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0334849857528701</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.00837607895158873</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.130659331395125</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.132052578965637</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.365135419757716</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.000373893073066147</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.027069676356541</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0966627805616126</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.138607631498054</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.000927474988395301</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.143375895739402</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.233538639319376</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.91332237852592</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.233704906519994</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.556608568742145</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.19243715512716</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.633071570090768</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.51395571495515</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.504588481660106</v>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -8612,91 +8964,97 @@
       </c>
       <c r="B17"/>
       <c r="C17" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.314962850545424</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.100374857267694</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.323857591498837</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0459412581829713</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0578096651171411</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0818676169398049</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0293885410878568</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.041728046652652</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.204264936932837</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.00681132392888474</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.00743692980912469</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0813347777210482</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.150802796062924</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.00591654338862635</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0268158280524225</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.096959286606789</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.113129553553935</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.000841471768419934</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.00649657729354201</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0355646538912295</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.395980775280769</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0193569325323502</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.272351407989928</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.546497591210454</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.272486581333375</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.142851126479745</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.601206044050032</v>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -8705,91 +9063,97 @@
       </c>
       <c r="B18"/>
       <c r="C18" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.768979628558757</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.124431143160102</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.279727733215322</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.193053714797203</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1381109025845</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.126429969506553</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0325490086798014</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.107649546441626</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.183689993989999</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.112216462199238</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.00141532562528259</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.0385813200052303</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.100929968394127</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.00672015447733912</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0376925192139727</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.063526397197148</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.104799481735209</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.00126057588599619</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.198548833747102</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.145736705774923</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1.27001995919068</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.376609187471825</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0428277135309251</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.229547067850421</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.184947102478878</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>-1.07835787419774</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.317629074077052</v>
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -8798,91 +9162,97 @@
       </c>
       <c r="B19"/>
       <c r="C19" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.620462075303386</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.176783550627939</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.217901049533148</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.179956622973416</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.112981521888056</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0936476749635413</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.022179419843872</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.038485335878367</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.212271608439113</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.105054220876667</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.00067289277251629</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.122148476589965</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.291530913756204</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.0169307840414787</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0360553862964996</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0503808377656664</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.096310570246564</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.00262858840756728</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.177450528167976</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.108011367473215</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.551703229896462</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.108024705221014</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.00336935671216099</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.540962018542131</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.540918287700821</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.097239763025374</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.120302301052945</v>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -8891,91 +9261,97 @@
       </c>
       <c r="B20"/>
       <c r="C20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.48763567853241</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.616859515859885</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.199745014756661</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.225203311385187</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0562223710966696</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0944311286144539</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.00688915070387816</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.116625972304991</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.177367948797788</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.100674585445191</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.000334428480009475</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0685412662956431</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.265981868394181</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.0668181934008458</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0341431987177175</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0440281009267043</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0553398426809612</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.000482072588307023</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.129230629327057</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0269325028981312</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36514053419834</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.260645339806046</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.182353315813527</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.418552017998313</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.599387275573155</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.505107918819142</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.131909647981055</v>
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -8984,91 +9360,97 @@
       </c>
       <c r="B21"/>
       <c r="C21" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0391776599722105</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.400018832161872</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.12773171469878</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.252405458375353</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0940309155497905</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.134337351020563</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0086455473042983</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.172879160426057</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.117318093228763</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.100513671211502</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.000172659142950679</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.151985066813612</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.120892449085871</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.0291085616047994</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0223558203170651</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0265684363093117</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0302912288977294</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.000449336507410447</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0697182110839856</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.122383164304816</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.224981090772891</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.664177582906974</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.343130330079457</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.344818493584733</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.68497645430841</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.245779962174332</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.229067420144575</v>
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -9077,91 +9459,97 @@
       </c>
       <c r="B22"/>
       <c r="C22" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.268200050561156</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.15987240907501</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.283507120401248</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.166570976445143</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.11495920209907</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.115307261317255</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.00649974282303079</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.207401686370098</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0818528253840725</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0969680156800284</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.616465872332888</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.0473407389018177</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.0281630611185205</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0150150468139017</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0106418570513199</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0297652241785434</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.000753165156961141</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.00596630086611831</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.114674036692568</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.545558752795156</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.346113605718694</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.672584610535546</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>-1.23724928173379</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>-1.90184374216626</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>-2.7935161006801</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.657856976765167</v>
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -9173,88 +9561,94 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.242068084901225</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.861211617504531</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.72326242138923</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0597576369702884</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0545997687640812</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.216923374445816</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.00303833121835111</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.192405035522612</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.129777924792912</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0949495613552628</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.932155758882926</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.071523996514511</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.0267370903938112</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0134831467879264</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0100206453912311</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0233356501478242</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.00238863660642365</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.181472618049022</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.134867187671917</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.058766635636648</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.04451306676911</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>-1.61554733557822</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>-1.4371728240577</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>-3.22354327531982</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>-2.12026357291406</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-1.16361292923734</v>
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -9266,88 +9660,94 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.758382452318353</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.301121179025133</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.573621561070564</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.127567540379306</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.109959834421406</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.233931922438709</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0223434615253195</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.028045575459215</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.109869351295643</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.00101193337338092</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.602565568739724</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.0474279904564795</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.0264334674541418</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0139545112674622</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0086306387520275</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0297549970186519</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.0011002361640645</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.23278510720022</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.016954725757266</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>-1.21830191708233</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.158798285738843</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.334220080256817</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.649376366995363</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.978090465541953</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>-2.03759409688544</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-1.79928843316349</v>
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -9359,88 +9759,94 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.07397105433932</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.362637955153845</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.300710506995726</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0826355911521568</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0214263085163258</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.142483137788292</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0151688512215269</v>
+        <v>-0.0103004782521672</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.046414268229299</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.10166404287993</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.000970325921589451</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.128331134564776</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.0370941122424084</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.00389812728397777</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0128484986125136</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0076726144240776</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0242646124776583</v>
+        <v>0.0000244384361911994</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.000983229004553713</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.19510719245062</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.0315397997182591</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.28054216223713</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.156066847256035</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.354064921294097</v>
+        <v>-0.010330697881111</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.199427541474361</v>
+        <v>0.0000243474441570246</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.152922832371015</v>
+        <v>-0.010270483480005</v>
       </c>
       <c r="AD25" t="n">
-        <v>-1.28368617712215</v>
+        <v>-0.010330697881111</v>
       </c>
       <c r="AE25" t="n">
-        <v>-2.05876498690044</v>
+        <v>-0.0000000909920339631221</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.01027048348</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>-0.00256762087000106</v>
       </c>
     </row>
     <row r="26">
@@ -9449,91 +9855,97 @@
       </c>
       <c r="B26"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.16625705714621</v>
+        <v>-1.2296355637729</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.264362767857094</v>
+        <v>0.117646740041994</v>
       </c>
       <c r="F26" t="n">
-        <v>0.242869201505272</v>
+        <v>0.0729221139568544</v>
       </c>
       <c r="G26" t="n">
-        <v>0.194261051438572</v>
+        <v>0.0303682084397064</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0431030078605316</v>
+        <v>0.0043558654732369</v>
       </c>
       <c r="I26" t="n">
-        <v>0.314515777091386</v>
+        <v>0.001381255362844</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0315113352815806</v>
+        <v>-0.0035654161645554</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.608744314546676</v>
+        <v>-0.186260540013211</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.0982711445275058</v>
+        <v>-0.0731785291796595</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.000960782164182661</v>
+        <v>-0.000013514171012669</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0451738239447765</v>
+        <v>0.00120827452475672</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0151025968268524</v>
+        <v>0.023704883486836</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.00273081610851882</v>
+        <v>-0.0000469065941550301</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0146408228761549</v>
+        <v>-0.000253894026530199</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.00724609284152218</v>
+        <v>-0.00013630366305209</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.00125291743599055</v>
+        <v>0.0210987712012386</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.000979645728103863</v>
+        <v>0.000447460936214362</v>
       </c>
       <c r="W26" t="n">
-        <v>0.116719686827921</v>
+        <v>0.000223640232524996</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.0359282712793087</v>
+        <v>-0.0104309838917672</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17345448239989</v>
+        <v>-1.31500220534884</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.271560193110773</v>
+        <v>0.203013381617927</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.824936705702305</v>
+        <v>0.105042880059626</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.592601624040412</v>
+        <v>-0.223267090727667</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.291744296021291</v>
+        <v>-0.117315683408469</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.19363858531041</v>
+        <v>0.103661624696783</v>
       </c>
       <c r="AE26" t="n">
-        <v>-1.06197631540281</v>
+        <v>-0.244365861928906</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-1.22930450713938</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>-0.309893747654845</v>
       </c>
     </row>
     <row r="27">
@@ -9542,34 +9954,34 @@
       </c>
       <c r="B27"/>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.199908406757872</v>
+        <v>0.174665842519457</v>
       </c>
       <c r="E27" t="n">
-        <v>1.02428403100791</v>
+        <v>-0.00120064348707802</v>
       </c>
       <c r="F27" t="n">
-        <v>0.234599804801746</v>
+        <v>0.147155210677801</v>
       </c>
       <c r="G27" t="n">
-        <v>0.15928587189327</v>
+        <v>-0.00478085917833653</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0354319110011004</v>
+        <v>0.0325490752211528</v>
       </c>
       <c r="I27" t="n">
-        <v>0.25154363993049</v>
+        <v>-0.000290033632574016</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0236645790439209</v>
+        <v>-0.0052701635944319</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.216125279439693</v>
+        <v>-0.091938205158739</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0130070807374411</v>
+        <v>0.000768295925706</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9581,52 +9993,58 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.132913390919242</v>
+        <v>-0.00032773146646959</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.017410528264858</v>
+        <v>0.0208942228560717</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.00223511236832679</v>
+        <v>0.00000258952091642967</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.00982172763539681</v>
+        <v>0.0000113807274978693</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.00645843383716623</v>
+        <v>0.00000748310485440985</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.00308365752099749</v>
+        <v>0.0174461064382648</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.00105212743667453</v>
+        <v>-0.0000665609460793171</v>
       </c>
       <c r="W27" t="n">
-        <v>0.095231774413017</v>
+        <v>-0.00705747922720099</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0272243466202854</v>
+        <v>0.0042632641598749</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.211334982899188</v>
+        <v>0.174953186373054</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.01285745486659</v>
+        <v>-0.0014879873406754</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.704361405759689</v>
+        <v>0.168861150004635</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.0474713812057168</v>
+        <v>-0.0557802274428949</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.812101759163106</v>
+        <v>0.113234755300251</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.03629419692888</v>
+        <v>0.169151183637209</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.022836872942074</v>
+        <v>-0.0732263338811596</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.286699954332629</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-0.238218759071688</v>
       </c>
     </row>
     <row r="28">
@@ -9635,34 +10053,34 @@
       </c>
       <c r="B28"/>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.10046863928065</v>
+        <v>0.004515233336015</v>
       </c>
       <c r="E28" t="n">
-        <v>0.524786766957344</v>
+        <v>-0.00119286999101301</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.016080347229363</v>
+        <v>0.141618632295248</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0138332480770833</v>
+        <v>-0.0024235505617541</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0279234859988991</v>
+        <v>0.0307691269471698</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0779306099692082</v>
+        <v>-0.0000901506086344039</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0196599148895334</v>
+        <v>-0.00514851501622302</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.0934887021613682</v>
+        <v>-0.0895124224137281</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0581514132169505</v>
+        <v>0.000732039122165296</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -9674,52 +10092,58 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.181915370704627</v>
+        <v>-0.00011223708165684</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0167983951850547</v>
+        <v>0.0192351533879784</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.00280936961711405</v>
+        <v>0.0000032548705940303</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.00668009000270352</v>
+        <v>0.0000077399644372398</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.00574107447962623</v>
+        <v>0.00000665184494139971</v>
       </c>
       <c r="U28" t="n">
-        <v>0.00426063987336252</v>
+        <v>0.0237076654628795</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.000862305916034598</v>
+        <v>-0.000024321193814924</v>
       </c>
       <c r="W28" t="n">
-        <v>0.0780527258116822</v>
+        <v>-0.007946115059426</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.0668754680395387</v>
+        <v>0.0023208406534061</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.078522352599924</v>
+        <v>0.00475056078514799</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.703777758837918</v>
+        <v>-0.001428197440146</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.095462520815779</v>
+        <v>0.164542600122426</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.162679117504951</v>
+        <v>-0.0514934344563509</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.317872398317736</v>
+        <v>0.112907530460929</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.94312780455573</v>
+        <v>0.164632750731061</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.722343602418219</v>
+        <v>-0.0752010999192304</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.116229893805932</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>-0.209161285620205</v>
       </c>
     </row>
     <row r="29">
@@ -9728,34 +10152,34 @@
       </c>
       <c r="B29"/>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.129417976809744</v>
+        <v>0.00329752530653399</v>
       </c>
       <c r="E29" t="n">
-        <v>0.300635009185592</v>
+        <v>-0.001353355623473</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0041478078390151</v>
+        <v>0.0710966738275662</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0295966736513301</v>
+        <v>-0.00181574602479632</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.001194639893219</v>
+        <v>-0.0024764036382978</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0522916142007128</v>
+        <v>0.0000606407595116973</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0169602089350546</v>
+        <v>-0.00506045063756709</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0510901318097985</v>
+        <v>-0.0873481991635286</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0929184631233055</v>
+        <v>0.000685969532293398</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -9767,52 +10191,58 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.190847621884019</v>
+        <v>-0.000109151490092791</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0156110721766536</v>
+        <v>0.0176799094709183</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.000293043010447602</v>
+        <v>0.000000339496733449049</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.00302862955485382</v>
+        <v>0.00000350891543183986</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.00316449350844382</v>
+        <v>0.00000366633432848009</v>
       </c>
       <c r="U29" t="n">
-        <v>0.00863155222093056</v>
+        <v>0.0209541976096495</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.000798225882717532</v>
+        <v>-0.000023615574997863</v>
       </c>
       <c r="W29" t="n">
-        <v>0.0324230937704803</v>
+        <v>-0.00681116501778001</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.00723125352726157</v>
+        <v>0.0009603878127673</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.006729571776105</v>
+        <v>0.00354496566052601</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.423323414219232</v>
+        <v>-0.00160079597746499</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.00276966820796601</v>
+        <v>0.0618144470339583</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.274767140068557</v>
+        <v>-0.053929240876856</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.331772799033737</v>
+        <v>0.00775090403789701</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.761825785029074</v>
+        <v>0.0617538062744466</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.23372159295603</v>
+        <v>-0.0748834384865058</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.00969507372095901</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>-0.204169896319964</v>
       </c>
     </row>
     <row r="30">
@@ -9821,34 +10251,34 @@
       </c>
       <c r="B30"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0648073627463605</v>
+        <v>0.00351657656975</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.283066809034289</v>
+        <v>-0.001260409240115</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.188720608190535</v>
+        <v>0.054172738924029</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0128674177652747</v>
+        <v>-0.00170723173699811</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0396974295194952</v>
+        <v>-0.0024393361168677</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.266873947521892</v>
+        <v>0.00031074713914403</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0198186839780425</v>
+        <v>-0.00492458642620059</v>
       </c>
       <c r="K30" t="n">
-        <v>0.245026053751842</v>
+        <v>0.0151945228846712</v>
       </c>
       <c r="L30" t="n">
-        <v>0.107332292506908</v>
+        <v>0.0657788206132981</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -9860,52 +10290,58 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.183157276623661</v>
+        <v>-0.00061146927372322</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.00676626739432467</v>
+        <v>0.0151212509278731</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.000285971658178611</v>
+        <v>0.000000331304356319994</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.00134676949436724</v>
+        <v>0.00000156029301218012</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.00177950937707208</v>
+        <v>0.00000206165870391003</v>
       </c>
       <c r="U30" t="n">
-        <v>0.00237422153404077</v>
+        <v>0.0140718579150378</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.000701321908712698</v>
+        <v>-0.000042740567043693</v>
       </c>
       <c r="W30" t="n">
-        <v>0.00702258007206789</v>
+        <v>-0.0399805069744474</v>
       </c>
       <c r="X30" t="n">
-        <v>0.0271904906616773</v>
+        <v>0.00279391822517053</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.037078241345632</v>
+        <v>0.003748676649698</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.384952413126282</v>
+        <v>-0.00149250932006201</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.383524631723849</v>
+        <v>0.045493006636902</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.574989041822441</v>
+        <v>0.072205339730441</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.252331433560245</v>
+        <v>0.118042415462978</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.095542738220404</v>
+        <v>0.045182259497758</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.911426262073317</v>
+        <v>0.058133481815403</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.120298582792612</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.133230876163033</v>
       </c>
     </row>
     <row r="31">
@@ -9914,34 +10350,34 @@
       </c>
       <c r="B31"/>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.28346045506663</v>
+        <v>0.0030091324203429</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.072444038757184</v>
+        <v>-0.001223362643267</v>
       </c>
       <c r="F31" t="n">
-        <v>0.554708072621966</v>
+        <v>0.05339430797514</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0165067083042643</v>
+        <v>-0.00159139040079221</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0670101490242839</v>
+        <v>-0.0024058743591114</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.36382241629954</v>
+        <v>0.000424415931046029</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0219895532180396</v>
+        <v>-0.00481765049970637</v>
       </c>
       <c r="K31" t="n">
-        <v>0.118320532496194</v>
+        <v>-0.0229354280635361</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0293505634648154</v>
+        <v>-0.0000103018052678098</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -9953,52 +10389,58 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.265383515321532</v>
+        <v>-0.00040344013302993</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0023425847898464</v>
+        <v>0.0147889242270675</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.000279608272315239</v>
+        <v>0.000000323932181351956</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.00101746593741716</v>
+        <v>0.00000117877271113001</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.00149740043885975</v>
+        <v>0.00000173481085786998</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.000323854182184991</v>
+        <v>0.00945690889479398</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.00048732428150576</v>
+        <v>-0.00000285834100818404</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.0032334194853993</v>
+        <v>-0.0013852788134272</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.0622999638433834</v>
+        <v>-0.0026083696727416</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.257466605367196</v>
+        <v>0.003227941292826</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.0984378884566171</v>
+        <v>-0.00144217151574999</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.296866286781522</v>
+        <v>0.045137213646553</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.34617975832759</v>
+        <v>-0.00310151620727911</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.705284755786757</v>
+        <v>0.041983454194124</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.349380261962944</v>
+        <v>0.044712797715506</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.489697778331836</v>
+        <v>-0.0125584251020731</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.0437692239712</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.072498193572676</v>
       </c>
     </row>
     <row r="32">
@@ -10007,34 +10449,34 @@
       </c>
       <c r="B32"/>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.178562163377217</v>
+        <v>0.003213566999166</v>
       </c>
       <c r="E32" t="n">
-        <v>0.240183191937857</v>
+        <v>-0.00127265112542299</v>
       </c>
       <c r="F32" t="n">
-        <v>0.182135000243182</v>
+        <v>0.0605986686598972</v>
       </c>
       <c r="G32" t="n">
-        <v>0.046682527171884</v>
+        <v>-0.00146682366058916</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0524719672331917</v>
+        <v>-0.002368772678518</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.386429275379733</v>
+        <v>0.000450977626010041</v>
       </c>
       <c r="J32" t="n">
-        <v>0.019802921504855</v>
+        <v>-0.00471794377005923</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0432505809845101</v>
+        <v>-0.0225017162871103</v>
       </c>
       <c r="L32" t="n">
-        <v>0.00960393426828406</v>
+        <v>-0.0000108247227220502</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -10046,52 +10488,58 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.330288061877299</v>
+        <v>-0.00000575006711854602</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.00338949350452501</v>
+        <v>0.014503516084081</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.000274164577999679</v>
+        <v>0.00000031762548597297</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.00100120816583779</v>
+        <v>0.00000115993715492997</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.00123761106939872</v>
+        <v>0.00000143382520621988</v>
       </c>
       <c r="U32" t="n">
-        <v>0.00503738545094546</v>
+        <v>-0.0198984688266725</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.000494963405012899</v>
+        <v>-0.000002793087780274</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.0562441131044229</v>
+        <v>-0.0001641508373288</v>
       </c>
       <c r="X32" t="n">
-        <v>0.0108066618654301</v>
+        <v>-0.0012159733233628</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.391048916073619</v>
+        <v>0.00341925808528901</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.452669944634259</v>
+        <v>-0.001478342211545</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.084865750824914</v>
+        <v>0.052687127955304</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.336266009630537</v>
+        <v>-0.0292920853869919</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.252213178210048</v>
+        <v>0.023288478551937</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.313834206770688</v>
+        <v>0.0522361503292932</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.332374378885575</v>
+        <v>-0.0093936165603194</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.0252293944256811</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.0497480687276139</v>
       </c>
     </row>
     <row r="33">
@@ -10100,34 +10548,34 @@
       </c>
       <c r="B33"/>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.423962517978124</v>
+        <v>0.005306727724218</v>
       </c>
       <c r="E33" t="n">
-        <v>0.116975946422978</v>
+        <v>-0.001248771643756</v>
       </c>
       <c r="F33" t="n">
-        <v>0.268579401561437</v>
+        <v>0.0599143375292739</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0734224024502885</v>
+        <v>-0.0013499189488351</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0957231778754999</v>
+        <v>-0.0023394001837589</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.42871696202656</v>
+        <v>0.000500732572405016</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0272517743704486</v>
+        <v>-0.00465569111149387</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0314167637831188</v>
+        <v>-0.0220030846902135</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.00449420339991824</v>
+        <v>-0.0000112993009829115</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -10139,52 +10587,58 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.205058890819514</v>
+        <v>-0.00010512432015042</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.037427549399739</v>
+        <v>0.0141958253750801</v>
       </c>
       <c r="R33" t="n">
-        <v>0.000198300178911062</v>
+        <v>-0.000000229732961338976</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.000992810208750326</v>
+        <v>0.00000115020752363185</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.000239999786936005</v>
+        <v>0.000000278044601943978</v>
       </c>
       <c r="U33" t="n">
-        <v>0.00394094650479018</v>
+        <v>-0.0179108773346862</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.000484029372340887</v>
+        <v>-0.00000272679389060195</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.0650195514059628</v>
+        <v>0.00155293149921217</v>
       </c>
       <c r="X33" t="n">
-        <v>0.0301621190197705</v>
+        <v>0.000604886595215201</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.651146480536181</v>
+        <v>0.00550155986109702</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.110208016135078</v>
+        <v>-0.00144360378063499</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.037141557933327</v>
+        <v>0.052275117487813</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.161998887097469</v>
+        <v>-0.0236779449141082</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.199753401969456</v>
+        <v>0.028528479256088</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.740691866370562</v>
+        <v>0.051774384915408</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.327090899220947</v>
+        <v>-0.00576706757942206</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.032586435336549</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.055470909131511</v>
       </c>
     </row>
     <row r="34">
@@ -10192,93 +10646,37 @@
         <v>67</v>
       </c>
       <c r="B34"/>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.1006414926096</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.221878079554261</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.147446342067959</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-0.0185525309733649</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0824818237452043</v>
-      </c>
-      <c r="I34" t="n">
-        <v>-0.616876171778661</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0206206466514326</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-0.0203318349881162</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.00264155034917435</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.196547150282437</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>-0.0162940448288468</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.000194363861199969</v>
-      </c>
-      <c r="S34" t="n">
-        <v>-0.000995798705676766</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>-0.000419613351686655</v>
-      </c>
-      <c r="W34" t="n">
-        <v>-0.081634709193796</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.0242509515984553</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0.055933813641926</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0.266585758521934</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>-0.384897359591596</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.10393518560558</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>-0.281073320295444</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.04144625186841</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.361338146743153</v>
-      </c>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+      <c r="S34"/>
+      <c r="T34"/>
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+      <c r="Y34"/>
+      <c r="Z34"/>
+      <c r="AA34"/>
+      <c r="AB34"/>
+      <c r="AC34"/>
+      <c r="AD34"/>
+      <c r="AE34"/>
+      <c r="AF34"/>
+      <c r="AG34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results/04-2026/beta/contributions-comparison-04-2026.xlsx
+++ b/results/04-2026/beta/contributions-comparison-04-2026.xlsx
@@ -2886,7 +2886,7 @@
         <v>-0.0289055700739013</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.499897395595688</v>
+        <v>-0.117350200113337</v>
       </c>
       <c r="G24" t="n">
         <v>-0.014530714174193</v>
@@ -2949,25 +2949,25 @@
         <v>-0.261464773606026</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.139229581720164</v>
+        <v>0.241898475197163</v>
       </c>
       <c r="AB24" t="n">
         <v>0.400833075000047</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.262180996866793</v>
+        <v>0.641727532450867</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.373161504158873</v>
+        <v>0.00796655275845429</v>
       </c>
       <c r="AE24" t="n">
         <v>0.430588072018699</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.26031492736318</v>
+        <v>0.639861462947255</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.089150923320437</v>
+        <v>0.00573571057558156</v>
       </c>
     </row>
     <row r="25">
@@ -2987,7 +2987,7 @@
         <v>-0.0733698868603123</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.403643992985071</v>
+        <v>0.013033349568796</v>
       </c>
       <c r="G25" t="n">
         <v>-0.030262516077315</v>
@@ -3050,25 +3050,25 @@
         <v>0.272737134010574</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.270169588737866</v>
+        <v>0.145924562447469</v>
       </c>
       <c r="AB25" t="n">
         <v>0.329046389863244</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.0598134793214488</v>
+        <v>0.47446466261275</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.412652726526158</v>
+        <v>0.00344142465917663</v>
       </c>
       <c r="AE25" t="n">
         <v>0.353311002340902</v>
       </c>
       <c r="AF25" t="n">
-        <v>-1.25792918345213</v>
+        <v>-0.843278000160834</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.531464333252592</v>
+        <v>-0.332914903533748</v>
       </c>
     </row>
     <row r="26">
@@ -3088,7 +3088,7 @@
         <v>-0.0710580054369052</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0501880171233495</v>
+        <v>0.239406622639966</v>
       </c>
       <c r="G26" t="n">
         <v>0.0586159262003014</v>
@@ -3151,25 +3151,25 @@
         <v>0.0657687568511386</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.463404670727734</v>
+        <v>0.651809176738972</v>
       </c>
       <c r="AB26" t="n">
         <v>-0.0604293144674622</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.463266623529774</v>
+        <v>0.651789683360029</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.148888893636348</v>
+        <v>0.337293399647586</v>
       </c>
       <c r="AE26" t="n">
         <v>-0.0591763970314716</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.828717102571314</v>
+        <v>1.01724016240157</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.15052163934381</v>
+        <v>0.0951585553325976</v>
       </c>
     </row>
     <row r="27">
@@ -3189,13 +3189,13 @@
         <v>-0.177384890887503</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0906545813014853</v>
+        <v>0.145349181392773</v>
       </c>
       <c r="G27" t="n">
         <v>-0.0135823615948663</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0530552985300118</v>
+        <v>0.0204825031770616</v>
       </c>
       <c r="I27" t="n">
         <v>0.25154363993049</v>
@@ -3252,25 +3252,25 @@
         <v>-0.0928836530179101</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.388300039888712</v>
+        <v>0.410384135092492</v>
       </c>
       <c r="AB27" t="n">
         <v>-0.0142040674807482</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.434153830494396</v>
+        <v>0.456241218675884</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.136756399958222</v>
+        <v>0.158840495162002</v>
       </c>
       <c r="AE27" t="n">
         <v>-0.0111204099597507</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0107249510890314</v>
+        <v>0.0328123392705189</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.0395430506071521</v>
+        <v>0.211658991114627</v>
       </c>
     </row>
     <row r="28">
@@ -3290,13 +3290,13 @@
         <v>-0.176236422781678</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0320613916729151</v>
+        <v>0.102231761871102</v>
       </c>
       <c r="G28" t="n">
         <v>-0.0140897876009744</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0611887191445801</v>
+        <v>0.0303844116342299</v>
       </c>
       <c r="I28" t="n">
         <v>0.0779306099692082</v>
@@ -3353,25 +3353,25 @@
         <v>-0.139873044970078</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.162760065763167</v>
+        <v>0.202085233703639</v>
       </c>
       <c r="AB28" t="n">
         <v>0.0811831420485551</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.303804069949841</v>
+        <v>0.343095608249406</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.0848294557939591</v>
+        <v>0.12415462373443</v>
       </c>
       <c r="AE28" t="n">
         <v>0.0769225021751926</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.0187752660882153</v>
+        <v>0.0205162722113488</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.109315598970001</v>
+        <v>0.0568226934306508</v>
       </c>
     </row>
     <row r="29">
@@ -3391,13 +3391,13 @@
         <v>-0.199946813675512</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0227724580374239</v>
+        <v>0.101672286414703</v>
       </c>
       <c r="G29" t="n">
         <v>-0.00902915102977396</v>
       </c>
       <c r="H29" t="n">
-        <v>0.024763706910763</v>
+        <v>0.0272086052503855</v>
       </c>
       <c r="I29" t="n">
         <v>-0.0522916142007128</v>
@@ -3454,25 +3454,25 @@
         <v>-0.140839771734219</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.0527043427898117</v>
+        <v>0.0742234180974693</v>
       </c>
       <c r="AB29" t="n">
         <v>0.104915517060876</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.112269577286512</v>
+        <v>0.239056667938165</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.000412728589098861</v>
+        <v>0.126515032298182</v>
       </c>
       <c r="AE29" t="n">
         <v>0.0962839648399452</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.19455309949128</v>
+        <v>-0.0677660088396269</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.156528422020213</v>
+        <v>0.250700691260953</v>
       </c>
     </row>
     <row r="30">
@@ -3492,13 +3492,13 @@
         <v>-0.186214773942108</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.291860335754416</v>
+        <v>-0.16686215403164</v>
       </c>
       <c r="G30" t="n">
         <v>-0.00871948653904214</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0345883706468194</v>
+        <v>0.0369848894040224</v>
       </c>
       <c r="I30" t="n">
         <v>-0.266873947521892</v>
@@ -3555,25 +3555,25 @@
         <v>-0.139951506095078</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.52666917896959</v>
+        <v>-0.398953680402588</v>
       </c>
       <c r="AB30" t="n">
         <v>0.18995088856399</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.275658655070582</v>
+        <v>-0.148199934352975</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.259795231447698</v>
+        <v>-0.132079732880696</v>
       </c>
       <c r="AE30" t="n">
         <v>0.187576667029949</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.575848947354461</v>
+        <v>-0.448390226636853</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.194613090461231</v>
+        <v>-0.115706905998653</v>
       </c>
     </row>
     <row r="31">
@@ -3593,13 +3593,13 @@
         <v>-0.18074145350152</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.15535957088525</v>
+        <v>-0.0313851804324279</v>
       </c>
       <c r="G31" t="n">
         <v>-0.00433211445750534</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0414325973251567</v>
+        <v>0.043787785295544</v>
       </c>
       <c r="I31" t="n">
         <v>-0.36382241629954</v>
@@ -3656,25 +3656,25 @@
         <v>-0.136187107329353</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.476931589288372</v>
+        <v>-0.350169750618483</v>
       </c>
       <c r="AB31" t="n">
         <v>0.0706728660628411</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.345900938412574</v>
+        <v>-0.219234135309988</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.113109172988833</v>
+        <v>0.0136526656810571</v>
       </c>
       <c r="AE31" t="n">
         <v>0.0709967202450261</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.624171173262917</v>
+        <v>-0.497504370160331</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.353337121549218</v>
+        <v>-0.248286083356366</v>
       </c>
     </row>
     <row r="32">
@@ -3694,13 +3694,13 @@
         <v>-0.188023408655981</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0910626909637126</v>
+        <v>0.0445220451969919</v>
       </c>
       <c r="G32" t="n">
         <v>-0.000926599399724825</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0369153856606749</v>
+        <v>0.0392387337096022</v>
       </c>
       <c r="I32" t="n">
         <v>-0.386429275379733</v>
@@ -3757,25 +3757,25 @@
         <v>-0.145161352331443</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.253608567858958</v>
+        <v>-0.297987909831869</v>
       </c>
       <c r="AB32" t="n">
         <v>0.0195130068435475</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.23404305869826</v>
+        <v>-0.278413218041402</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.132820707520774</v>
+        <v>0.0884413655478634</v>
       </c>
       <c r="AE32" t="n">
         <v>0.014475621392602</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.52622116360248</v>
+        <v>-0.570591322945622</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.480198595927784</v>
+        <v>-0.396062982145609</v>
       </c>
     </row>
     <row r="33">
@@ -3795,13 +3795,13 @@
         <v>-0.184495417794735</v>
       </c>
       <c r="F33" t="n">
-        <v>0.128834675525228</v>
+        <v>0.0625721612707403</v>
       </c>
       <c r="G33" t="n">
         <v>0.0107213802706063</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0416283220440629</v>
+        <v>0.0439168865394133</v>
       </c>
       <c r="I33" t="n">
         <v>-0.42871696202656</v>
@@ -3858,25 +3858,25 @@
         <v>-0.143061358041577</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.240484032811458</v>
+        <v>-0.304709825738888</v>
       </c>
       <c r="AB33" t="n">
         <v>-0.00912811548088149</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.249635464504215</v>
+        <v>-0.313867481114126</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.188232929215102</v>
+        <v>0.124007136287672</v>
       </c>
       <c r="AE33" t="n">
         <v>-0.0130690619856717</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.606126865059347</v>
+        <v>-0.670358881669258</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.583092037319801</v>
+        <v>-0.546711200353016</v>
       </c>
     </row>
     <row r="34">
@@ -3896,13 +3896,13 @@
         <v>-0.183578043716544</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0139896774285151</v>
+        <v>-0.0621279186476758</v>
       </c>
       <c r="G34" t="n">
         <v>0.00704988013781239</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0233003782332651</v>
+        <v>0.0255593448966518</v>
       </c>
       <c r="I34" t="n">
         <v>-0.616876171778661</v>
@@ -3959,25 +3959,25 @@
         <v>-0.143181122174836</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.589995381969783</v>
+        <v>-0.636152946721656</v>
       </c>
       <c r="AB34" t="n">
         <v>-0.10280007135667</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.693438933785944</v>
+        <v>-0.739646784072489</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.0268807898088781</v>
+        <v>-0.0192767749429954</v>
       </c>
       <c r="AE34" t="n">
         <v>-0.10280007135667</v>
       </c>
       <c r="AF34" t="n">
-        <v>-1.08215840470343</v>
+        <v>-1.12836625498998</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.709669401657044</v>
+        <v>-0.716705207441297</v>
       </c>
     </row>
   </sheetData>
@@ -6444,7 +6444,7 @@
         <v>0.142483137788292</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0187005366381567</v>
+        <v>0.00840005838598947</v>
       </c>
       <c r="K25" t="n">
         <v>0.137992081379504</v>
@@ -6477,7 +6477,7 @@
         <v>-0.0076726144240776</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0242890509138495</v>
+        <v>-0.0242646124776583</v>
       </c>
       <c r="V25" t="n">
         <v>-0.0000531438557844164</v>
@@ -6495,25 +6495,25 @@
         <v>0.272737134010574</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.259838890856755</v>
+        <v>-0.270169588737866</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.329022042419087</v>
+        <v>0.329046389863244</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.0700839628014538</v>
+        <v>0.0598134793214488</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.402322028645047</v>
+        <v>-0.412652726526158</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.353311093332936</v>
+        <v>0.353311002340902</v>
       </c>
       <c r="AF25" t="n">
-        <v>-1.24765869997213</v>
+        <v>-1.25792918345213</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.528896712382591</v>
+        <v>-0.531464333252592</v>
       </c>
     </row>
     <row r="26">
@@ -6521,100 +6521,100 @@
         <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.66614404825135</v>
+        <v>0.436508484478446</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.188704745478899</v>
+        <v>-0.0710580054369052</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0227340968335049</v>
+        <v>0.0501880171233495</v>
       </c>
       <c r="G26" t="n">
-        <v>0.028247717760595</v>
+        <v>0.0586159262003014</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0230908327045624</v>
+        <v>0.0274466981777993</v>
       </c>
       <c r="I26" t="n">
-        <v>0.313134521728542</v>
+        <v>0.314515777091386</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0167727057307057</v>
+        <v>0.0132072895661503</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0399401532635637</v>
+        <v>-0.226200693276775</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0328468378633532</v>
+        <v>-0.0403316913163063</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.000947267993169992</v>
+        <v>-0.000960782164182661</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.0102942452796516</v>
+        <v>-0.00908597075489488</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.019590885584065</v>
+        <v>0.00411399790277102</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.00268390951436379</v>
+        <v>-0.00273081610851882</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0143869288496247</v>
+        <v>-0.0146408228761549</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.00710978917847009</v>
+        <v>-0.00724609284152218</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0223516886372291</v>
+        <v>-0.00125291743599055</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.000517122684655328</v>
+        <v>-0.0000696617484409661</v>
       </c>
       <c r="W26" t="n">
-        <v>0.22476206195789</v>
+        <v>0.224985702190415</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0229002032225388</v>
+        <v>0.0124692193307716</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.61468392753924</v>
+        <v>0.299681722190402</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.137244624766788</v>
+        <v>0.0657687568511386</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.358361790668108</v>
+        <v>0.463404670727734</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.162837776260205</v>
+        <v>-0.0604293144674622</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.580582306938243</v>
+        <v>0.463266623529774</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.0452272689395654</v>
+        <v>0.148888893636348</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.185189464897434</v>
+        <v>-0.0591763970314716</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05802160971069</v>
+        <v>0.828717102571314</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.159372108311035</v>
+        <v>-0.15052163934381</v>
       </c>
     </row>
     <row r="27">
@@ -6628,31 +6628,31 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.420709831037319</v>
+        <v>-0.246043988517862</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.176184247400425</v>
+        <v>-0.177384890887503</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0565006293763161</v>
+        <v>0.0906545813014853</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.00880150241652977</v>
+        <v>-0.0135823615948663</v>
       </c>
       <c r="H27" t="n">
-        <v>0.020506223308859</v>
+        <v>0.0530552985300118</v>
       </c>
       <c r="I27" t="n">
-        <v>0.251833673563064</v>
+        <v>0.25154363993049</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0123004390178763</v>
+        <v>0.0070302754234444</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.18964298329505</v>
+        <v>-0.281581188453789</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0473865174312755</v>
+        <v>0.0481548133569815</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -6664,58 +6664,58 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.00899748036153736</v>
+        <v>-0.00932521182800695</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.0144565211050625</v>
+        <v>0.00643770175100916</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.00223770188924322</v>
+        <v>-0.00223511236832679</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.00983310836289468</v>
+        <v>-0.00982172763539681</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.00646591694202064</v>
+        <v>-0.00645843383716623</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0205297639592623</v>
+        <v>-0.00308365752099749</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.000434869020035866</v>
+        <v>-0.000501429966115183</v>
       </c>
       <c r="W27" t="n">
-        <v>0.214079581465423</v>
+        <v>0.207022102238222</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0322655618445932</v>
+        <v>0.0365288260044681</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.505498412760509</v>
+        <v>-0.330545226387455</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.0913956656772347</v>
+        <v>-0.0928836530179101</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.219438889884077</v>
+        <v>0.388300039888712</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.0415761599621467</v>
+        <v>-0.0142040674807482</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.320919075194145</v>
+        <v>0.434153830494396</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.0323947836789873</v>
+        <v>0.136756399958222</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.0621059239214089</v>
+        <v>-0.0111204099597507</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.275975003243598</v>
+        <v>0.0107249510890314</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.198675708464536</v>
+        <v>-0.0395430506071521</v>
       </c>
     </row>
     <row r="28">
@@ -6729,31 +6729,31 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.150858146592394</v>
+        <v>-0.146342913256379</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.175043552790665</v>
+        <v>-0.176236422781678</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.109557240622333</v>
+        <v>0.0320613916729151</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0116662370392203</v>
+        <v>-0.0140897876009744</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0304195921974103</v>
+        <v>0.0611887191445801</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0780207605778426</v>
+        <v>0.0779306099692082</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0108989230434262</v>
+        <v>0.00575040802720318</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.00546385491572805</v>
+        <v>-0.0949762773294562</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0544809327441534</v>
+        <v>0.0552129718663187</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -6765,58 +6765,58 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.00970680057072466</v>
+        <v>-0.0098190376523815</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.0126215734177798</v>
+        <v>0.00661357997019864</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.00281262448770808</v>
+        <v>-0.00280936961711405</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.00668782996714076</v>
+        <v>-0.00668009000270352</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.00574772632456763</v>
+        <v>-0.00574107447962623</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.019447025589517</v>
+        <v>0.00426063987336252</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.000402619731988997</v>
+        <v>-0.000426940925803921</v>
       </c>
       <c r="W28" t="n">
-        <v>0.170716249234254</v>
+        <v>0.162770134174828</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.0297158643115744</v>
+        <v>-0.0273950236581683</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.187456851853127</v>
+        <v>-0.182706291067979</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.138444847529932</v>
+        <v>-0.139873044970078</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.00178253435925942</v>
+        <v>0.162760065763167</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.132676576504906</v>
+        <v>0.0811831420485551</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.190896539488912</v>
+        <v>0.303804069949841</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.079803294937102</v>
+        <v>0.0848294557939591</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.152123602094423</v>
+        <v>0.0769225021751926</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.135005159894147</v>
+        <v>-0.0187752660882153</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.099845686650204</v>
+        <v>-0.109315598970001</v>
       </c>
     </row>
     <row r="29">
@@ -6830,31 +6830,31 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.110173388408814</v>
+        <v>-0.10687586310228</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.198593458052039</v>
+        <v>-0.199946813675512</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0938691318649901</v>
+        <v>-0.0227724580374239</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.00721340500497764</v>
+        <v>-0.00902915102977396</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0272401105490608</v>
+        <v>0.024763706910763</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0523522549602245</v>
+        <v>-0.0522916142007128</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0116792142668356</v>
+        <v>0.00661876362926851</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0351930300938164</v>
+        <v>-0.0521551690697122</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0589448427500478</v>
+        <v>0.0596308122823412</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -6866,58 +6866,58 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.00922620457866887</v>
+        <v>-0.00933535606876166</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.00855857232959935</v>
+        <v>0.00912133714131898</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.000293382507181051</v>
+        <v>-0.000293043010447602</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.00303213847028566</v>
+        <v>-0.00302862955485382</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.0031681598427723</v>
+        <v>-0.00316449350844382</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.0123226453887189</v>
+        <v>0.00863155222093056</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.000371559930609723</v>
+        <v>-0.000395175505607586</v>
       </c>
       <c r="W29" t="n">
-        <v>0.116915450722698</v>
+        <v>0.110104285704918</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.0152025009432854</v>
+        <v>-0.0142421131305181</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.169527870704099</v>
+        <v>-0.165982905043573</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.139238975756754</v>
+        <v>-0.140839771734219</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.11451878982377</v>
+        <v>-0.0527043427898117</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.158844757937732</v>
+        <v>0.104915517060876</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.104518673248615</v>
+        <v>0.112269577286512</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.0621665348635455</v>
+        <v>-0.000412728589098861</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.171167403326451</v>
+        <v>0.0962839648399452</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.204248173212239</v>
+        <v>-0.19455309949128</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.360698318340177</v>
+        <v>0.156528422020213</v>
       </c>
     </row>
     <row r="30">
@@ -6931,31 +6931,31 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.11749209491152</v>
+        <v>-0.11397551834177</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.184954364701993</v>
+        <v>-0.186214773942108</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.346033074678445</v>
+        <v>-0.291860335754416</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.00701225480204403</v>
+        <v>-0.00871948653904214</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0370277067636871</v>
+        <v>0.0345883706468194</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.267184694661036</v>
+        <v>-0.266873947521892</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0117504457810699</v>
+        <v>0.00682585935486931</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0295327400207467</v>
+        <v>0.0447272629054179</v>
       </c>
       <c r="L30" t="n">
-        <v>0.00839718520675031</v>
+        <v>0.0741760058200484</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -6967,58 +6967,58 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.00442812281376111</v>
+        <v>-0.00503959208748433</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.00792813540768285</v>
+        <v>0.00719311552019024</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.000286302962534931</v>
+        <v>-0.000285971658178611</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.00134832978737942</v>
+        <v>-0.00134676949436724</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.00178157103577599</v>
+        <v>-0.00177950937707208</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.011697636380997</v>
+        <v>0.00237422153404077</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.000322956686060288</v>
+        <v>-0.000365697253103981</v>
       </c>
       <c r="W30" t="n">
-        <v>0.114722443042679</v>
+        <v>0.0747419360682316</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.00711649746668697</v>
+        <v>-0.00432257924151644</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.163987462838498</v>
+        <v>-0.1602387861888</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.138458996775016</v>
+        <v>-0.139951506095078</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.572162185606492</v>
+        <v>-0.52666917896959</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.117745548833549</v>
+        <v>0.18995088856399</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.39370107053356</v>
+        <v>-0.275658655070582</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.304977490945456</v>
+        <v>-0.259795231447698</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.129443185214546</v>
+        <v>0.187576667029949</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.696147530147073</v>
+        <v>-0.575848947354461</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.327843966624264</v>
+        <v>-0.194613090461231</v>
       </c>
     </row>
     <row r="31">
@@ -7032,31 +7032,31 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.100537913769166</v>
+        <v>-0.0975287813488231</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.179518090858253</v>
+        <v>-0.18074145350152</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.20875387886039</v>
+        <v>-0.15535957088525</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.00274072405671313</v>
+        <v>-0.00433211445750534</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0438384716842681</v>
+        <v>0.0414325973251567</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.364246832230586</v>
+        <v>-0.36382241629954</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0103326017155023</v>
+        <v>0.00551495121579593</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0366137137752495</v>
+        <v>0.0136782857117134</v>
       </c>
       <c r="L31" t="n">
-        <v>0.00890406050198482</v>
+        <v>0.00889375869671701</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -7068,58 +7068,58 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.00142312480846168</v>
+        <v>-0.00182656494149161</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.00805673466147888</v>
+        <v>0.00673218956558858</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.000279932204496591</v>
+        <v>-0.000279608272315239</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.00101864471012829</v>
+        <v>-0.00101746593741716</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.00149913524971762</v>
+        <v>-0.00149740043885975</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.00978076307697897</v>
+        <v>-0.000323854182184991</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.000315600107555253</v>
+        <v>-0.000318458448563437</v>
       </c>
       <c r="W31" t="n">
-        <v>0.0616095842025686</v>
+        <v>0.0602243053891414</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.0109793532176722</v>
+        <v>-0.0135877228904138</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.145311068813816</v>
+        <v>-0.14208312752099</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.134744935813603</v>
+        <v>-0.136187107329353</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.522068802934925</v>
+        <v>-0.476931589288372</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.0737743822701202</v>
+        <v>0.0706728660628411</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.387884392606698</v>
+        <v>-0.345900938412574</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.157821970704339</v>
+        <v>-0.113109172988833</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.0835551453470992</v>
+        <v>0.0709967202450261</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.667940397234117</v>
+        <v>-0.624171173262917</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.425835315121894</v>
+        <v>-0.353337121549218</v>
       </c>
     </row>
     <row r="32">
@@ -7133,31 +7133,31 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.107368263247405</v>
+        <v>-0.104154696248239</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.186750757530558</v>
+        <v>-0.188023408655981</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0304640223038154</v>
+        <v>0.0910626909637126</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000540224260864334</v>
+        <v>-0.000926599399724825</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0392841583391929</v>
+        <v>0.0369153856606749</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.386880253005743</v>
+        <v>-0.386429275379733</v>
       </c>
       <c r="J32" t="n">
-        <v>0.00998641367971701</v>
+        <v>0.00526846990965778</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0380736733973169</v>
+        <v>0.0155719571102066</v>
       </c>
       <c r="L32" t="n">
-        <v>0.00935610800823099</v>
+        <v>0.00934528328550894</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -7169,58 +7169,58 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.000358589023948943</v>
+        <v>0.000352838956830397</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.00827285943507663</v>
+        <v>0.00623065664900438</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.000274482203485652</v>
+        <v>-0.000274164577999679</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.00100236810299272</v>
+        <v>-0.00100120816583779</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.00123904489460494</v>
+        <v>-0.00123761106939872</v>
       </c>
       <c r="U32" t="n">
-        <v>0.024935854277618</v>
+        <v>0.00503738545094546</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.000309363502687192</v>
+        <v>-0.000312156590467466</v>
       </c>
       <c r="W32" t="n">
-        <v>0.009435814340737</v>
+        <v>0.0092716635034082</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.0222591298571621</v>
+        <v>-0.0234751031805249</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.150436010658066</v>
+        <v>-0.147016752572777</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.143683010119898</v>
+        <v>-0.145161352331443</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.306295695814262</v>
+        <v>-0.253608567858958</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.0488050922305394</v>
+        <v>0.0195130068435475</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.257331537250197</v>
+        <v>-0.23404305869826</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0805845571914808</v>
+        <v>0.132820707520774</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.0238692379529214</v>
+        <v>0.014475621392602</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.551450558028161</v>
+        <v>-0.52622116360248</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.529946664655398</v>
+        <v>-0.480198595927784</v>
       </c>
     </row>
     <row r="33">
@@ -7234,31 +7234,31 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.177302710484615</v>
+        <v>-0.171995982760397</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.183246646150979</v>
+        <v>-0.184495417794735</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0689203379959541</v>
+        <v>0.128834675525228</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0120712992194414</v>
+        <v>0.0107213802706063</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0439677222278218</v>
+        <v>0.0416283220440629</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.429217694598965</v>
+        <v>-0.42871696202656</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0109394892890476</v>
+        <v>0.00628379817755373</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00242889478013606</v>
+        <v>-0.0195741899100774</v>
       </c>
       <c r="L33" t="n">
-        <v>0.00976637754758537</v>
+        <v>0.00975507824660246</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -7270,96 +7270,160 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00259276018795545</v>
+        <v>0.00248763586780503</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.00564681216626738</v>
+        <v>0.0085490132088127</v>
       </c>
       <c r="R33" t="n">
-        <v>0.000198529911872401</v>
+        <v>0.000198300178911062</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.000993960416273958</v>
+        <v>-0.000992810208750326</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.000240277831537949</v>
+        <v>-0.000239999786936005</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0218518238394764</v>
+        <v>0.00394094650479018</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.000302765050606375</v>
+        <v>-0.000305491844496977</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.00291588534563375</v>
+        <v>-0.00136295384642158</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.0121918619904309</v>
+        <v>-0.0115869753952157</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.218931602374652</v>
+        <v>-0.213430042513555</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.141617754260942</v>
+        <v>-0.143061358041577</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.292759150299271</v>
+        <v>-0.240484032811458</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0145498294332267</v>
+        <v>-0.00912811548088149</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.278163943760303</v>
+        <v>-0.249635464504215</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.136458544299694</v>
+        <v>0.188232929215102</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.00730199440624964</v>
+        <v>-0.0130690619856717</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.638713300395896</v>
+        <v>-0.606126865059347</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.638562946451312</v>
+        <v>-0.583092037319801</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
         <v>67</v>
       </c>
-      <c r="B34"/>
-      <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="H34"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-      <c r="S34"/>
-      <c r="T34"/>
-      <c r="U34"/>
-      <c r="V34"/>
-      <c r="W34"/>
-      <c r="X34"/>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34"/>
-      <c r="AB34"/>
-      <c r="AC34"/>
-      <c r="AD34"/>
-      <c r="AE34"/>
-      <c r="AF34"/>
-      <c r="AG34"/>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.205141427200942</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.183578043716544</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.0139896774285151</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.00704988013781239</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0233003782332651</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.616876171778661</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.0103444268268873</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.0919261259634657</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0101430800572218</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.00208389012354234</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.00342021698030483</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.000194363861199969</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-0.000995798705676766</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-0.000299428155345378</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-0.0331773637149976</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.00776152455226643</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-0.245538348742651</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-0.143181122174836</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-0.589995381969783</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-0.10280007135667</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>-0.693438933785944</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.0268807898088781</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>-0.10280007135667</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>-1.08215840470343</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>-0.709669401657044</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9666,7 +9730,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.382547195482351</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9729,25 +9793,25 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>0.381128056917327</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>0.379546535584074</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>0.381128056917327</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>0.379546535584075</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>0.0948866338960186</v>
       </c>
     </row>
     <row r="25">
@@ -9765,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.416677342553867</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -9777,7 +9841,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0103004782521672</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -9810,7 +9874,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0000244384361911994</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -9828,25 +9892,25 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.010330697881111</v>
+        <v>0.416094151185335</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.0000243474441570246</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.010270483480005</v>
+        <v>0.414651183291301</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.010330697881111</v>
+        <v>0.416094151185335</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.0000000909920339631221</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.01027048348</v>
+        <v>0.414651183291296</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.00256762087000106</v>
+        <v>0.198549429718844</v>
       </c>
     </row>
     <row r="26">
@@ -9855,97 +9919,97 @@
       </c>
       <c r="B26"/>
       <c r="C26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2296355637729</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.117646740041994</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0729221139568544</v>
+        <v>0.189218605516617</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0303682084397064</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0043558654732369</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001381255362844</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0035654161645554</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.186260540013211</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.0731785291796595</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.000013514171012669</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.00120827452475672</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.023704883486836</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.0000469065941550301</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.000253894026530199</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.00013630366305209</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0210987712012386</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.000447460936214362</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.000223640232524996</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.0104309838917672</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>-1.31500220534884</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.203013381617927</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.105042880059626</v>
+        <v>0.188404506011238</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.223267090727667</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.117315683408469</v>
+        <v>0.188523059830255</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.103661624696783</v>
+        <v>0.188404506011238</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.244365861928906</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>-1.22930450713938</v>
+        <v>0.188523059830256</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.309893747654845</v>
+        <v>0.245680194676408</v>
       </c>
     </row>
     <row r="27">
@@ -9957,31 +10021,31 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.174665842519457</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.00120064348707802</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.147155210677801</v>
+        <v>0.0546946000912877</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.00478085917833653</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0325490752211528</v>
+        <v>-0.0325727953529502</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.000290033632574016</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0052701635944319</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.091938205158739</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.000768295925706</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9993,58 +10057,58 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.00032773146646959</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0208942228560717</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.00000258952091642967</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0000113807274978693</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.00000748310485440985</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0174461064382648</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.0000665609460793171</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.00705747922720099</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0042632641598749</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.174953186373054</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.0014879873406754</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.168861150004635</v>
+        <v>0.02208409520378</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.0557802274428949</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.113234755300251</v>
+        <v>0.022087388181488</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.169151183637209</v>
+        <v>0.02208409520378</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.0732263338811596</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.286699954332629</v>
+        <v>0.0220873881814875</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.238218759071688</v>
+        <v>0.251202041721779</v>
       </c>
     </row>
     <row r="28">
@@ -10056,31 +10120,31 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.004515233336015</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.00119286999101301</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.141618632295248</v>
+        <v>0.0701703701981869</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0024235505617541</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0307691269471698</v>
+        <v>-0.0308043075103502</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0000901506086344039</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.00514851501622302</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.0895124224137281</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.000732039122165296</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -10092,58 +10156,58 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.00011223708165684</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0192351533879784</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0000032548705940303</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0000077399644372398</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.00000665184494139971</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0237076654628795</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.000024321193814924</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.007946115059426</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.0023208406534061</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.00475056078514799</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.001428197440146</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.164542600122426</v>
+        <v>0.039325167940472</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.0514934344563509</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.112907530460929</v>
+        <v>0.039291538299565</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.164632750731061</v>
+        <v>0.0393251679404709</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.0752010999192304</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.116229893805932</v>
+        <v>0.0392915382995641</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.209161285620205</v>
+        <v>0.166138292400652</v>
       </c>
     </row>
     <row r="29">
@@ -10155,31 +10219,31 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00329752530653399</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.001353355623473</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0710966738275662</v>
+        <v>0.124444744452127</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.00181574602479632</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0024764036382978</v>
+        <v>0.0024448983396225</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0000606407595116973</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.00506045063756709</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0873481991635286</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.000685969532293398</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -10191,58 +10255,58 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.000109151490092791</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0176799094709183</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.000000339496733449049</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.00000350891543183986</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.00000366633432848009</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0.0209541976096495</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.000023615574997863</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.00681116501778001</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.0009603878127673</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.00354496566052601</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.00160079597746499</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.0618144470339583</v>
+        <v>0.126927760887281</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.053929240876856</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.00775090403789701</v>
+        <v>0.126787090651653</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.0617538062744466</v>
+        <v>0.126927760887281</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.0748834384865058</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.00969507372095901</v>
+        <v>0.126787090651653</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.204169896319964</v>
+        <v>0.09417226924074</v>
       </c>
     </row>
     <row r="30">
@@ -10254,31 +10318,31 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00351657656975</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.001260409240115</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.054172738924029</v>
+        <v>0.124998181722776</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.00170723173699811</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0024393361168677</v>
+        <v>0.002396518757203</v>
       </c>
       <c r="I30" t="n">
-        <v>0.00031074713914403</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.00492458642620059</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0151945228846712</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0657788206132981</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -10290,58 +10354,58 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.00061146927372322</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0151212509278731</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.000000331304356319994</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.00000156029301218012</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.00000206165870391003</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0140718579150378</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.000042740567043693</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.0399805069744474</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.00279391822517053</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.003748676649698</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.00149250932006201</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.045493006636902</v>
+        <v>0.127715498567002</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.072205339730441</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.118042415462978</v>
+        <v>0.127458720717607</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.045182259497758</v>
+        <v>0.127715498567002</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.058133481815403</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.120298582792612</v>
+        <v>0.127458720717608</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.133230876163033</v>
+        <v>0.078906184462578</v>
       </c>
     </row>
     <row r="31">
@@ -10353,31 +10417,31 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0030091324203429</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.001223362643267</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.05339430797514</v>
+        <v>0.123974390452822</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.00159139040079221</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0024058743591114</v>
+        <v>0.0023551879703873</v>
       </c>
       <c r="I31" t="n">
-        <v>0.000424415931046029</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.00481765049970637</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.0229354280635361</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.0000103018052678098</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -10389,58 +10453,58 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.00040344013302993</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0147889242270675</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.000000323932181351956</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00000117877271113001</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.00000173481085786998</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0.00945690889479398</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.00000285834100818404</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.0013852788134272</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.0026083696727416</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.003227941292826</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.00144217151574999</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.045137213646553</v>
+        <v>0.126761838669889</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.00310151620727911</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.041983454194124</v>
+        <v>0.126666803102586</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.044712797715506</v>
+        <v>0.12676183866989</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.0125584251020731</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0437692239712</v>
+        <v>0.126666803102586</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.072498193572676</v>
+        <v>0.105051038192852</v>
       </c>
     </row>
     <row r="32">
@@ -10452,31 +10516,31 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.003213566999166</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.00127265112542299</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0605986686598972</v>
+        <v>-0.0465406457667207</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.00146682366058916</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.002368772678518</v>
+        <v>0.0023233480489273</v>
       </c>
       <c r="I32" t="n">
-        <v>0.000450977626010041</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.00471794377005923</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0225017162871103</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.0000108247227220502</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -10488,58 +10552,58 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.00000575006711854602</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.014503516084081</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.00000031762548597297</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00000115993715492997</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.00000143382520621988</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.0198984688266725</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.000002793087780274</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.0001641508373288</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.0012159733233628</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.00341925808528901</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.001478342211545</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.052687127955304</v>
+        <v>-0.044379341972911</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.0292920853869919</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.023288478551937</v>
+        <v>-0.044370159343142</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0522361503292932</v>
+        <v>-0.0443793419729106</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.0093936165603194</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.0252293944256811</v>
+        <v>-0.044370159343142</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.0497480687276139</v>
+        <v>0.084135613782175</v>
       </c>
     </row>
     <row r="33">
@@ -10551,31 +10615,31 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.005306727724218</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.001248771643756</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0599143375292739</v>
+        <v>-0.0662625142544877</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0013499189488351</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.0023394001837589</v>
+        <v>0.0022885644953504</v>
       </c>
       <c r="I33" t="n">
-        <v>0.000500732572405016</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.00465569111149387</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0220030846902135</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.0000112993009829115</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -10587,58 +10651,58 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.00010512432015042</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0141958253750801</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.000000229732961338976</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00000115020752363185</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.000000278044601943978</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.0179108773346862</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.00000272679389060195</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.00155293149921217</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.000604886595215201</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00550155986109702</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.00144360378063499</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.052275117487813</v>
+        <v>-0.06422579292743</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.0236779449141082</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.028528479256088</v>
+        <v>-0.064232016609911</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.051774384915408</v>
+        <v>-0.06422579292743</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.00576706757942206</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.032586435336549</v>
+        <v>-0.0642320166099111</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.055470909131511</v>
+        <v>0.036380836966785</v>
       </c>
     </row>
     <row r="34">
@@ -10646,37 +10710,99 @@
         <v>67</v>
       </c>
       <c r="B34"/>
-      <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="H34"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-      <c r="S34"/>
-      <c r="T34"/>
-      <c r="U34"/>
-      <c r="V34"/>
-      <c r="W34"/>
-      <c r="X34"/>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34"/>
-      <c r="AB34"/>
-      <c r="AC34"/>
-      <c r="AD34"/>
-      <c r="AE34"/>
-      <c r="AF34"/>
-      <c r="AG34"/>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.0481382412191607</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0022589666633867</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-0.046157564751873</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>-0.0462078502865449</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>-0.0461575647518735</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>-0.0462078502865499</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>-0.007035805784253</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
